--- a/3k2s/Экономика IT-компании/Лабораторная работа 2_ФОТ_с.xlsx
+++ b/3k2s/Экономика IT-компании/Лабораторная работа 2_ФОТ_с.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Институт\Экономика ERP\Лабораторные работы студенты\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\General\BELSTU\3k2s\Экономика IT-компании\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20633" windowHeight="7598"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="Задание исх данные, решение 1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -936,10 +945,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -952,271 +960,245 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1499,1927 +1481,2289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L101"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="59.59765625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.69921875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.296875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.69921875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.19921875" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="1" width="59.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="95"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="77"/>
+    </row>
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="90"/>
+      <c r="B4" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="80"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="B5" s="67">
-        <v>1</v>
-      </c>
-      <c r="C5" s="68">
-        <v>2</v>
-      </c>
-      <c r="D5" s="68">
-        <v>3</v>
-      </c>
-      <c r="E5" s="68">
+      <c r="A5" s="4"/>
+      <c r="B5" s="56">
+        <v>1</v>
+      </c>
+      <c r="C5" s="57">
+        <v>2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>3</v>
+      </c>
+      <c r="E5" s="57">
         <v>4</v>
       </c>
-      <c r="F5" s="68">
+      <c r="F5" s="57">
         <v>5</v>
       </c>
-      <c r="G5" s="68">
+      <c r="G5" s="57">
         <v>6</v>
       </c>
-      <c r="H5" s="68">
+      <c r="H5" s="57">
         <v>7</v>
       </c>
-      <c r="I5" s="68">
+      <c r="I5" s="57">
         <v>8</v>
       </c>
-      <c r="J5" s="68">
+      <c r="J5" s="57">
         <v>9</v>
       </c>
-      <c r="K5" s="68">
+      <c r="K5" s="57">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="9">
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7">
         <v>365</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>365</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>366</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>365</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="7">
         <v>365</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="7">
         <v>366</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="7">
         <v>365</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="7">
         <v>365</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <v>366</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="7">
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9">
+    <row r="7" spans="1:11" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7">
         <v>113</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>112</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>111</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>110</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="7">
         <v>109</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="7">
         <v>108</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="7">
         <v>113</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="7">
         <v>112</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="7">
         <v>111</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="7">
         <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8">
+        <f>C6-C7</f>
+        <v>253</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-    </row>
-    <row r="10" spans="1:11" ht="16.7" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8">
+        <f>SUM(C10:C13)</f>
+        <v>32</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <v>26</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <v>28</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <v>30</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <v>31</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <v>32</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <v>28</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="9">
         <v>26</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <v>27</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="9">
         <v>30</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="9">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="25" t="s">
+    <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="9">
-        <v>3</v>
-      </c>
-      <c r="C11" s="11">
-        <v>1</v>
-      </c>
-      <c r="D11" s="11">
-        <v>2</v>
-      </c>
-      <c r="E11" s="11">
+      <c r="B11" s="7">
+        <v>3</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9">
         <v>0</v>
       </c>
-      <c r="F11" s="11">
-        <v>3</v>
-      </c>
-      <c r="G11" s="11">
-        <v>2</v>
-      </c>
-      <c r="H11" s="11">
-        <v>1</v>
-      </c>
-      <c r="I11" s="11">
-        <v>2</v>
-      </c>
-      <c r="J11" s="11">
-        <v>3</v>
-      </c>
-      <c r="K11" s="11">
+      <c r="F11" s="9">
+        <v>3</v>
+      </c>
+      <c r="G11" s="9">
+        <v>2</v>
+      </c>
+      <c r="H11" s="9">
+        <v>1</v>
+      </c>
+      <c r="I11" s="9">
+        <v>2</v>
+      </c>
+      <c r="J11" s="9">
+        <v>3</v>
+      </c>
+      <c r="K11" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
+    <row r="12" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="9">
-        <v>3</v>
-      </c>
-      <c r="C12" s="11">
-        <v>2</v>
-      </c>
-      <c r="D12" s="11">
-        <v>1</v>
-      </c>
-      <c r="E12" s="11">
+      <c r="B12" s="7">
+        <v>3</v>
+      </c>
+      <c r="C12" s="9">
+        <v>2</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9">
         <v>4</v>
       </c>
-      <c r="F12" s="11">
-        <v>2</v>
-      </c>
-      <c r="G12" s="11">
-        <v>1</v>
-      </c>
-      <c r="H12" s="11">
-        <v>3</v>
-      </c>
-      <c r="I12" s="11">
-        <v>2</v>
-      </c>
-      <c r="J12" s="11">
-        <v>3</v>
-      </c>
-      <c r="K12" s="11">
+      <c r="F12" s="9">
+        <v>2</v>
+      </c>
+      <c r="G12" s="9">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9">
+        <v>3</v>
+      </c>
+      <c r="I12" s="9">
+        <v>2</v>
+      </c>
+      <c r="J12" s="9">
+        <v>3</v>
+      </c>
+      <c r="K12" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="9">
-        <v>2</v>
-      </c>
-      <c r="C13" s="9">
-        <v>1</v>
-      </c>
-      <c r="D13" s="9">
-        <v>2</v>
-      </c>
-      <c r="E13" s="9">
+      <c r="B13" s="7">
+        <v>2</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2</v>
+      </c>
+      <c r="E13" s="7">
         <v>0</v>
       </c>
-      <c r="F13" s="9">
-        <v>3</v>
-      </c>
-      <c r="G13" s="9">
+      <c r="F13" s="7">
+        <v>3</v>
+      </c>
+      <c r="G13" s="7">
         <v>0</v>
       </c>
-      <c r="H13" s="9">
-        <v>2</v>
-      </c>
-      <c r="I13" s="9">
-        <v>1</v>
-      </c>
-      <c r="J13" s="9">
-        <v>3</v>
-      </c>
-      <c r="K13" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="H13" s="7">
+        <v>2</v>
+      </c>
+      <c r="I13" s="7">
+        <v>1</v>
+      </c>
+      <c r="J13" s="7">
+        <v>3</v>
+      </c>
+      <c r="K13" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8">
+        <f>C8-C9</f>
+        <v>221</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:11" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8">
+        <f>C14*8</f>
+        <v>1768</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="7">
         <v>10</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="7">
         <v>9</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="7">
         <v>28</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="7">
         <v>7</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="7">
         <v>15</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="7">
         <v>6</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="7">
         <v>10</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="7">
         <v>15</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="7">
         <v>10</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="7">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-    </row>
-    <row r="18" spans="1:11" ht="29.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8">
+        <f>C15-C16</f>
+        <v>1759</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="1:11" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8">
+        <f>C17/12</f>
+        <v>146.58333333333334</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
     </row>
     <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
     </row>
     <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
-      <c r="K21" s="90"/>
+      <c r="B21" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="80"/>
     </row>
     <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="B22" s="67">
-        <v>1</v>
-      </c>
-      <c r="C22" s="68">
-        <v>2</v>
-      </c>
-      <c r="D22" s="68">
-        <v>3</v>
-      </c>
-      <c r="E22" s="68">
+      <c r="A22" s="4"/>
+      <c r="B22" s="56">
+        <v>1</v>
+      </c>
+      <c r="C22" s="57">
+        <v>2</v>
+      </c>
+      <c r="D22" s="57">
+        <v>3</v>
+      </c>
+      <c r="E22" s="57">
         <v>4</v>
       </c>
-      <c r="F22" s="68">
+      <c r="F22" s="57">
         <v>5</v>
       </c>
-      <c r="G22" s="68">
+      <c r="G22" s="57">
         <v>6</v>
       </c>
-      <c r="H22" s="68">
+      <c r="H22" s="57">
         <v>7</v>
       </c>
-      <c r="I22" s="68">
+      <c r="I22" s="57">
         <v>8</v>
       </c>
-      <c r="J22" s="68">
+      <c r="J22" s="57">
         <v>9</v>
       </c>
-      <c r="K22" s="68">
+      <c r="K22" s="57">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>600</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="7">
         <v>520</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="7">
         <v>480</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="7">
         <v>660</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="7">
         <v>500</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="7">
         <v>450</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="7">
         <v>390</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="7">
         <v>670</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="7">
         <v>580</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="7">
         <v>490</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="7">
         <v>50</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="7">
         <v>55</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="7">
         <v>60</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="7">
         <v>40</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="7">
         <v>45</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="7">
         <v>50</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="7">
         <v>55</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="7">
         <v>60</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="7">
         <v>45</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="7">
         <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="9">
-        <v>2</v>
-      </c>
-      <c r="C25" s="9">
-        <v>3</v>
-      </c>
-      <c r="D25" s="9">
-        <v>2</v>
-      </c>
-      <c r="E25" s="9">
-        <v>3</v>
-      </c>
-      <c r="F25" s="9">
-        <v>2</v>
-      </c>
-      <c r="G25" s="9">
-        <v>3</v>
-      </c>
-      <c r="H25" s="9">
-        <v>2</v>
-      </c>
-      <c r="I25" s="9">
-        <v>3</v>
-      </c>
-      <c r="J25" s="9">
-        <v>2</v>
-      </c>
-      <c r="K25" s="9">
+      <c r="B25" s="7">
+        <v>2</v>
+      </c>
+      <c r="C25" s="7">
+        <v>3</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3</v>
+      </c>
+      <c r="F25" s="7">
+        <v>2</v>
+      </c>
+      <c r="G25" s="7">
+        <v>3</v>
+      </c>
+      <c r="H25" s="7">
+        <v>2</v>
+      </c>
+      <c r="I25" s="7">
+        <v>3</v>
+      </c>
+      <c r="J25" s="7">
+        <v>2</v>
+      </c>
+      <c r="K25" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="7">
         <v>13380</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="7">
         <v>15960</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="7">
         <v>16040</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="7">
         <v>27300</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="7">
         <v>38420</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="7">
         <v>4760</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="7">
         <v>23500</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="7">
         <v>19450</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="7">
         <v>21360</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="7">
         <v>14790</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="23">
-        <v>1</v>
-      </c>
-      <c r="C28" s="24">
-        <v>2</v>
-      </c>
-      <c r="D28" s="24">
-        <v>3</v>
-      </c>
-      <c r="E28" s="24">
+      <c r="B28" s="20">
+        <v>1</v>
+      </c>
+      <c r="C28" s="21">
+        <v>2</v>
+      </c>
+      <c r="D28" s="21">
+        <v>3</v>
+      </c>
+      <c r="E28" s="21">
         <v>4</v>
       </c>
-      <c r="F28" s="24">
-        <v>2</v>
-      </c>
-      <c r="G28" s="24">
-        <v>1</v>
-      </c>
-      <c r="H28" s="24">
+      <c r="F28" s="21">
+        <v>2</v>
+      </c>
+      <c r="G28" s="21">
+        <v>1</v>
+      </c>
+      <c r="H28" s="21">
         <v>4</v>
       </c>
-      <c r="I28" s="24">
-        <v>3</v>
-      </c>
-      <c r="J28" s="9">
-        <v>3</v>
-      </c>
-      <c r="K28" s="9">
+      <c r="I28" s="21">
+        <v>3</v>
+      </c>
+      <c r="J28" s="7">
+        <v>3</v>
+      </c>
+      <c r="K28" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="20">
         <v>5</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="21">
         <v>4</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="21">
         <v>5</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="21">
         <v>6</v>
       </c>
-      <c r="F29" s="24">
-        <v>3</v>
-      </c>
-      <c r="G29" s="24">
+      <c r="F29" s="21">
+        <v>3</v>
+      </c>
+      <c r="G29" s="21">
         <v>4</v>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="21">
         <v>5</v>
       </c>
-      <c r="I29" s="24">
+      <c r="I29" s="21">
         <v>6</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="7">
         <v>4</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="23">
-        <v>1</v>
-      </c>
-      <c r="C30" s="24">
-        <v>1</v>
-      </c>
-      <c r="D30" s="24">
-        <v>2</v>
-      </c>
-      <c r="E30" s="24">
-        <v>1</v>
-      </c>
-      <c r="F30" s="24">
-        <v>2</v>
-      </c>
-      <c r="G30" s="24">
-        <v>3</v>
-      </c>
-      <c r="H30" s="24">
-        <v>2</v>
-      </c>
-      <c r="I30" s="24">
-        <v>1</v>
-      </c>
-      <c r="J30" s="9">
-        <v>2</v>
-      </c>
-      <c r="K30" s="9">
+      <c r="B30" s="20">
+        <v>1</v>
+      </c>
+      <c r="C30" s="21">
+        <v>1</v>
+      </c>
+      <c r="D30" s="21">
+        <v>2</v>
+      </c>
+      <c r="E30" s="21">
+        <v>1</v>
+      </c>
+      <c r="F30" s="21">
+        <v>2</v>
+      </c>
+      <c r="G30" s="21">
+        <v>3</v>
+      </c>
+      <c r="H30" s="21">
+        <v>2</v>
+      </c>
+      <c r="I30" s="21">
+        <v>1</v>
+      </c>
+      <c r="J30" s="7">
+        <v>2</v>
+      </c>
+      <c r="K30" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="23">
-        <v>1</v>
-      </c>
-      <c r="C31" s="24">
-        <v>2</v>
-      </c>
-      <c r="D31" s="24">
-        <v>3</v>
-      </c>
-      <c r="E31" s="24">
-        <v>1</v>
-      </c>
-      <c r="F31" s="24">
-        <v>2</v>
-      </c>
-      <c r="G31" s="24">
-        <v>3</v>
-      </c>
-      <c r="H31" s="24">
-        <v>1</v>
-      </c>
-      <c r="I31" s="24">
-        <v>2</v>
-      </c>
-      <c r="J31" s="9">
-        <v>3</v>
-      </c>
-      <c r="K31" s="9">
+      <c r="B31" s="20">
+        <v>1</v>
+      </c>
+      <c r="C31" s="21">
+        <v>2</v>
+      </c>
+      <c r="D31" s="21">
+        <v>3</v>
+      </c>
+      <c r="E31" s="21">
+        <v>1</v>
+      </c>
+      <c r="F31" s="21">
+        <v>2</v>
+      </c>
+      <c r="G31" s="21">
+        <v>3</v>
+      </c>
+      <c r="H31" s="21">
+        <v>1</v>
+      </c>
+      <c r="I31" s="21">
+        <v>2</v>
+      </c>
+      <c r="J31" s="7">
+        <v>3</v>
+      </c>
+      <c r="K31" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="23">
-        <v>2</v>
-      </c>
-      <c r="C32" s="24">
-        <v>2</v>
-      </c>
-      <c r="D32" s="24">
-        <v>3</v>
-      </c>
-      <c r="E32" s="24">
-        <v>1</v>
-      </c>
-      <c r="F32" s="24">
-        <v>3</v>
-      </c>
-      <c r="G32" s="24">
-        <v>2</v>
-      </c>
-      <c r="H32" s="24">
-        <v>2</v>
-      </c>
-      <c r="I32" s="24">
-        <v>3</v>
-      </c>
-      <c r="J32" s="9">
-        <v>1</v>
-      </c>
-      <c r="K32" s="9">
+      <c r="B32" s="20">
+        <v>2</v>
+      </c>
+      <c r="C32" s="21">
+        <v>2</v>
+      </c>
+      <c r="D32" s="21">
+        <v>3</v>
+      </c>
+      <c r="E32" s="21">
+        <v>1</v>
+      </c>
+      <c r="F32" s="21">
+        <v>3</v>
+      </c>
+      <c r="G32" s="21">
+        <v>2</v>
+      </c>
+      <c r="H32" s="21">
+        <v>2</v>
+      </c>
+      <c r="I32" s="21">
+        <v>3</v>
+      </c>
+      <c r="J32" s="7">
+        <v>1</v>
+      </c>
+      <c r="K32" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="23">
-        <v>3</v>
-      </c>
-      <c r="C33" s="24">
-        <v>1</v>
-      </c>
-      <c r="D33" s="24">
-        <v>2</v>
-      </c>
-      <c r="E33" s="24">
-        <v>1</v>
-      </c>
-      <c r="F33" s="24">
-        <v>3</v>
-      </c>
-      <c r="G33" s="24">
-        <v>2</v>
-      </c>
-      <c r="H33" s="24">
-        <v>2</v>
-      </c>
-      <c r="I33" s="24">
-        <v>1</v>
-      </c>
-      <c r="J33" s="9">
-        <v>3</v>
-      </c>
-      <c r="K33" s="9">
+      <c r="B33" s="20">
+        <v>3</v>
+      </c>
+      <c r="C33" s="21">
+        <v>1</v>
+      </c>
+      <c r="D33" s="21">
+        <v>2</v>
+      </c>
+      <c r="E33" s="21">
+        <v>1</v>
+      </c>
+      <c r="F33" s="21">
+        <v>3</v>
+      </c>
+      <c r="G33" s="21">
+        <v>2</v>
+      </c>
+      <c r="H33" s="21">
+        <v>2</v>
+      </c>
+      <c r="I33" s="21">
+        <v>1</v>
+      </c>
+      <c r="J33" s="7">
+        <v>3</v>
+      </c>
+      <c r="K33" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="23">
         <v>6</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="24">
         <v>7</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="24">
         <v>6</v>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="24">
         <v>5</v>
       </c>
-      <c r="F35" s="27">
+      <c r="F35" s="24">
         <v>8</v>
       </c>
-      <c r="G35" s="27">
+      <c r="G35" s="24">
         <v>8</v>
       </c>
-      <c r="H35" s="27">
+      <c r="H35" s="24">
         <v>7</v>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="24">
         <v>6</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="7">
         <v>7</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="7">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="23">
         <v>4</v>
       </c>
-      <c r="C36" s="27">
-        <v>3</v>
-      </c>
-      <c r="D36" s="27">
+      <c r="C36" s="24">
+        <v>3</v>
+      </c>
+      <c r="D36" s="24">
         <v>4</v>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="24">
         <v>4</v>
       </c>
-      <c r="F36" s="27">
-        <v>3</v>
-      </c>
-      <c r="G36" s="27">
+      <c r="F36" s="24">
+        <v>3</v>
+      </c>
+      <c r="G36" s="24">
         <v>4</v>
       </c>
-      <c r="H36" s="27">
-        <v>3</v>
-      </c>
-      <c r="I36" s="27">
+      <c r="H36" s="24">
+        <v>3</v>
+      </c>
+      <c r="I36" s="24">
         <v>4</v>
       </c>
-      <c r="J36" s="9">
-        <v>3</v>
-      </c>
-      <c r="K36" s="9">
+      <c r="J36" s="7">
+        <v>3</v>
+      </c>
+      <c r="K36" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="23">
         <v>5</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="24">
         <v>5</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="24">
         <v>4</v>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="24">
         <v>6</v>
       </c>
-      <c r="F37" s="27">
+      <c r="F37" s="24">
         <v>5</v>
       </c>
-      <c r="G37" s="27">
+      <c r="G37" s="24">
         <v>5</v>
       </c>
-      <c r="H37" s="27">
+      <c r="H37" s="24">
         <v>4</v>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="24">
         <v>6</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="7">
         <v>5</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="23">
         <v>7</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="24">
         <v>6</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="24">
         <v>8</v>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="24">
         <v>5</v>
       </c>
-      <c r="F38" s="27">
+      <c r="F38" s="24">
         <v>6</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="24">
         <v>7</v>
       </c>
-      <c r="H38" s="27">
+      <c r="H38" s="24">
         <v>8</v>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="24">
         <v>5</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="7">
         <v>6</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="7">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="26">
-        <v>3</v>
-      </c>
-      <c r="C39" s="27">
-        <v>2</v>
-      </c>
-      <c r="D39" s="27">
-        <v>3</v>
-      </c>
-      <c r="E39" s="27">
-        <v>2</v>
-      </c>
-      <c r="F39" s="27">
-        <v>2</v>
-      </c>
-      <c r="G39" s="27">
-        <v>3</v>
-      </c>
-      <c r="H39" s="27">
-        <v>2</v>
-      </c>
-      <c r="I39" s="27">
-        <v>3</v>
-      </c>
-      <c r="J39" s="9">
-        <v>2</v>
-      </c>
-      <c r="K39" s="9">
+      <c r="B39" s="23">
+        <v>3</v>
+      </c>
+      <c r="C39" s="24">
+        <v>2</v>
+      </c>
+      <c r="D39" s="24">
+        <v>3</v>
+      </c>
+      <c r="E39" s="24">
+        <v>2</v>
+      </c>
+      <c r="F39" s="24">
+        <v>2</v>
+      </c>
+      <c r="G39" s="24">
+        <v>3</v>
+      </c>
+      <c r="H39" s="24">
+        <v>2</v>
+      </c>
+      <c r="I39" s="24">
+        <v>3</v>
+      </c>
+      <c r="J39" s="7">
+        <v>2</v>
+      </c>
+      <c r="K39" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="26">
-        <v>2</v>
-      </c>
-      <c r="C40" s="27">
-        <v>2</v>
-      </c>
-      <c r="D40" s="27">
-        <v>3</v>
-      </c>
-      <c r="E40" s="27">
-        <v>1</v>
-      </c>
-      <c r="F40" s="27">
-        <v>2</v>
-      </c>
-      <c r="G40" s="27">
-        <v>2</v>
-      </c>
-      <c r="H40" s="27">
-        <v>1</v>
-      </c>
-      <c r="I40" s="27">
-        <v>3</v>
-      </c>
-      <c r="J40" s="9">
-        <v>2</v>
-      </c>
-      <c r="K40" s="9">
+      <c r="B40" s="23">
+        <v>2</v>
+      </c>
+      <c r="C40" s="24">
+        <v>2</v>
+      </c>
+      <c r="D40" s="24">
+        <v>3</v>
+      </c>
+      <c r="E40" s="24">
+        <v>1</v>
+      </c>
+      <c r="F40" s="24">
+        <v>2</v>
+      </c>
+      <c r="G40" s="24">
+        <v>2</v>
+      </c>
+      <c r="H40" s="24">
+        <v>1</v>
+      </c>
+      <c r="I40" s="24">
+        <v>3</v>
+      </c>
+      <c r="J40" s="7">
+        <v>2</v>
+      </c>
+      <c r="K40" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="60" t="s">
+      <c r="A41" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
     </row>
     <row r="42" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="23">
-        <v>1</v>
-      </c>
-      <c r="C42" s="24">
-        <v>2</v>
-      </c>
-      <c r="D42" s="24">
-        <v>1</v>
-      </c>
-      <c r="E42" s="24">
-        <v>2</v>
-      </c>
-      <c r="F42" s="24">
-        <v>1</v>
-      </c>
-      <c r="G42" s="24">
-        <v>2</v>
-      </c>
-      <c r="H42" s="24">
-        <v>1</v>
-      </c>
-      <c r="I42" s="24">
-        <v>2</v>
-      </c>
-      <c r="J42" s="9">
-        <v>1</v>
-      </c>
-      <c r="K42" s="9">
+      <c r="B42" s="20">
+        <v>1</v>
+      </c>
+      <c r="C42" s="21">
+        <v>2</v>
+      </c>
+      <c r="D42" s="21">
+        <v>1</v>
+      </c>
+      <c r="E42" s="21">
+        <v>2</v>
+      </c>
+      <c r="F42" s="21">
+        <v>1</v>
+      </c>
+      <c r="G42" s="21">
+        <v>2</v>
+      </c>
+      <c r="H42" s="21">
+        <v>1</v>
+      </c>
+      <c r="I42" s="21">
+        <v>2</v>
+      </c>
+      <c r="J42" s="7">
+        <v>1</v>
+      </c>
+      <c r="K42" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B43" s="23">
-        <v>1</v>
-      </c>
-      <c r="C43" s="24">
-        <v>2</v>
-      </c>
-      <c r="D43" s="24">
-        <v>3</v>
-      </c>
-      <c r="E43" s="24">
-        <v>1</v>
-      </c>
-      <c r="F43" s="24">
-        <v>2</v>
-      </c>
-      <c r="G43" s="24">
-        <v>3</v>
-      </c>
-      <c r="H43" s="24">
-        <v>1</v>
-      </c>
-      <c r="I43" s="24">
-        <v>2</v>
-      </c>
-      <c r="J43" s="9">
-        <v>3</v>
-      </c>
-      <c r="K43" s="9">
-        <v>1</v>
-      </c>
-      <c r="L43" s="38"/>
+      <c r="B43" s="20">
+        <v>1</v>
+      </c>
+      <c r="C43" s="21">
+        <v>2</v>
+      </c>
+      <c r="D43" s="21">
+        <v>3</v>
+      </c>
+      <c r="E43" s="21">
+        <v>1</v>
+      </c>
+      <c r="F43" s="21">
+        <v>2</v>
+      </c>
+      <c r="G43" s="21">
+        <v>3</v>
+      </c>
+      <c r="H43" s="21">
+        <v>1</v>
+      </c>
+      <c r="I43" s="21">
+        <v>2</v>
+      </c>
+      <c r="J43" s="7">
+        <v>3</v>
+      </c>
+      <c r="K43" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="23">
-        <v>2</v>
-      </c>
-      <c r="C44" s="24">
-        <v>3</v>
-      </c>
-      <c r="D44" s="24">
-        <v>1</v>
-      </c>
-      <c r="E44" s="24">
-        <v>2</v>
-      </c>
-      <c r="F44" s="24">
-        <v>3</v>
-      </c>
-      <c r="G44" s="24">
-        <v>1</v>
-      </c>
-      <c r="H44" s="24">
-        <v>2</v>
-      </c>
-      <c r="I44" s="24">
-        <v>3</v>
-      </c>
-      <c r="J44" s="9">
-        <v>1</v>
-      </c>
-      <c r="K44" s="9">
-        <v>2</v>
-      </c>
-      <c r="L44" s="29"/>
+      <c r="B44" s="20">
+        <v>2</v>
+      </c>
+      <c r="C44" s="21">
+        <v>3</v>
+      </c>
+      <c r="D44" s="21">
+        <v>1</v>
+      </c>
+      <c r="E44" s="21">
+        <v>2</v>
+      </c>
+      <c r="F44" s="21">
+        <v>3</v>
+      </c>
+      <c r="G44" s="21">
+        <v>1</v>
+      </c>
+      <c r="H44" s="21">
+        <v>2</v>
+      </c>
+      <c r="I44" s="21">
+        <v>3</v>
+      </c>
+      <c r="J44" s="7">
+        <v>1</v>
+      </c>
+      <c r="K44" s="7">
+        <v>2</v>
+      </c>
+      <c r="L44" s="26"/>
     </row>
     <row r="45" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="61" t="s">
+      <c r="A45" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="B45" s="23"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="24"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="38"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
     </row>
     <row r="46" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B46" s="20">
         <v>3500</v>
       </c>
-      <c r="C46" s="24">
+      <c r="C46" s="21">
         <v>3100</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D46" s="21">
         <v>3150</v>
       </c>
-      <c r="E46" s="24">
+      <c r="E46" s="21">
         <v>2900</v>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="21">
         <v>2180</v>
       </c>
-      <c r="G46" s="24">
+      <c r="G46" s="21">
         <v>3010</v>
       </c>
-      <c r="H46" s="24">
+      <c r="H46" s="21">
         <v>2240</v>
       </c>
-      <c r="I46" s="24">
+      <c r="I46" s="21">
         <v>2670</v>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="7">
         <v>2550</v>
       </c>
-      <c r="K46" s="9">
+      <c r="K46" s="7">
         <v>3140</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B47" s="20">
         <v>3160</v>
       </c>
-      <c r="C47" s="24">
+      <c r="C47" s="21">
         <v>2800</v>
       </c>
-      <c r="D47" s="24">
+      <c r="D47" s="21">
         <v>2750</v>
       </c>
-      <c r="E47" s="24">
+      <c r="E47" s="21">
         <v>2210</v>
       </c>
-      <c r="F47" s="24">
+      <c r="F47" s="21">
         <v>1800</v>
       </c>
-      <c r="G47" s="24">
+      <c r="G47" s="21">
         <v>2460</v>
       </c>
-      <c r="H47" s="24">
+      <c r="H47" s="21">
         <v>1900</v>
       </c>
-      <c r="I47" s="24">
+      <c r="I47" s="21">
         <v>2300</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="7">
         <v>2040</v>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="7">
         <v>2760</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="25" t="s">
+      <c r="A48" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B48" s="20">
         <v>2900</v>
       </c>
-      <c r="C48" s="24">
+      <c r="C48" s="21">
         <v>2580</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="21">
         <v>2400</v>
       </c>
-      <c r="E48" s="24">
+      <c r="E48" s="21">
         <v>2030</v>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="21">
         <v>1750</v>
       </c>
-      <c r="G48" s="24">
+      <c r="G48" s="21">
         <v>2170</v>
       </c>
-      <c r="H48" s="24">
+      <c r="H48" s="21">
         <v>1710</v>
       </c>
-      <c r="I48" s="24">
+      <c r="I48" s="21">
         <v>2055</v>
       </c>
-      <c r="J48" s="9">
+      <c r="J48" s="7">
         <v>1880</v>
       </c>
-      <c r="K48" s="9">
+      <c r="K48" s="7">
         <v>2255</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="15"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="18"/>
+      <c r="A49" s="13"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
     </row>
     <row r="50" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="96" t="s">
+      <c r="A50" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="96"/>
-      <c r="C50" s="96"/>
-      <c r="D50" s="96"/>
-      <c r="E50" s="96"/>
-      <c r="F50" s="96"/>
-      <c r="G50" s="96"/>
-      <c r="H50" s="96"/>
+      <c r="B50" s="81"/>
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
     </row>
     <row r="51" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="14">
-        <v>1</v>
-      </c>
-      <c r="C51" s="14">
-        <v>2</v>
-      </c>
-      <c r="D51" s="14">
-        <v>3</v>
-      </c>
-      <c r="E51" s="14">
+      <c r="B51" s="12">
+        <v>1</v>
+      </c>
+      <c r="C51" s="12">
+        <v>2</v>
+      </c>
+      <c r="D51" s="12">
+        <v>3</v>
+      </c>
+      <c r="E51" s="12">
         <v>4</v>
       </c>
-      <c r="F51" s="14">
+      <c r="F51" s="12">
         <v>5</v>
       </c>
-      <c r="G51" s="14">
+      <c r="G51" s="12">
         <v>6</v>
       </c>
-      <c r="H51" s="14">
+      <c r="H51" s="12">
         <v>7</v>
       </c>
-      <c r="I51" s="16">
+      <c r="I51" s="12">
         <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
+      <c r="B52" s="18">
+        <f>C23/C18</f>
+        <v>3.5474701534963047</v>
+      </c>
+      <c r="C52" s="18">
+        <f>B52*C53</f>
+        <v>4.1150653780557134</v>
+      </c>
+      <c r="D52" s="18">
+        <f>B52*D53</f>
+        <v>4.7890847072200113</v>
+      </c>
+      <c r="E52" s="18">
+        <f>B52*E53</f>
+        <v>5.5695281409891981</v>
+      </c>
+      <c r="F52" s="18">
+        <f>B52*F53</f>
+        <v>6.1371233655486073</v>
+      </c>
+      <c r="G52" s="18">
+        <f>B52*G53</f>
+        <v>6.7401932916429788</v>
+      </c>
+      <c r="H52" s="18">
+        <f>B52*H53</f>
+        <v>7.2013644115974982</v>
+      </c>
+      <c r="I52" s="18">
+        <f>B52*I53</f>
+        <v>7.6980102330869808</v>
+      </c>
     </row>
     <row r="53" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="51">
-        <v>1</v>
-      </c>
-      <c r="C53" s="52">
+      <c r="B53" s="41">
+        <v>1</v>
+      </c>
+      <c r="C53" s="42">
         <v>1.1599999999999999</v>
       </c>
-      <c r="D53" s="52">
+      <c r="D53" s="42">
         <v>1.35</v>
       </c>
-      <c r="E53" s="52">
+      <c r="E53" s="42">
         <v>1.57</v>
       </c>
-      <c r="F53" s="52">
+      <c r="F53" s="42">
         <v>1.73</v>
       </c>
-      <c r="G53" s="52">
+      <c r="G53" s="42">
         <v>1.9</v>
       </c>
-      <c r="H53" s="52">
+      <c r="H53" s="42">
         <v>2.0299999999999998</v>
       </c>
-      <c r="I53" s="52">
+      <c r="I53" s="42">
         <v>2.17</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="53"/>
-      <c r="B54" s="55"/>
-      <c r="C54" s="56"/>
-      <c r="D54" s="56"/>
-      <c r="E54" s="56"/>
-      <c r="F54" s="56"/>
-      <c r="G54" s="56"/>
-      <c r="H54" s="56"/>
-      <c r="I54" s="56"/>
-      <c r="J54" s="38"/>
+      <c r="A54" s="43"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="46"/>
+      <c r="I54" s="46"/>
     </row>
     <row r="55" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="92" t="s">
+      <c r="A55" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="B55" s="92"/>
-      <c r="C55" s="92"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="92"/>
-      <c r="F55" s="92"/>
-      <c r="G55" s="92"/>
-      <c r="H55" s="92"/>
-      <c r="I55" s="92"/>
-    </row>
-    <row r="56" spans="1:11" ht="32.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="85" t="s">
+      <c r="B55" s="74"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="74"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="74"/>
+    </row>
+    <row r="56" spans="1:11" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="B56" s="85" t="s">
+      <c r="B56" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="C56" s="85"/>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85" t="s">
+      <c r="C56" s="82"/>
+      <c r="D56" s="82"/>
+      <c r="E56" s="82"/>
+      <c r="F56" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="G56" s="85"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-    </row>
-    <row r="57" spans="1:11" ht="36.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="85"/>
-      <c r="B57" s="84" t="s">
+      <c r="G56" s="82"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+    </row>
+    <row r="57" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="82"/>
+      <c r="B57" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="85" t="s">
+      <c r="C57" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="85"/>
-      <c r="E57" s="84" t="s">
+      <c r="D57" s="82"/>
+      <c r="E57" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F57" s="85" t="s">
+      <c r="F57" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="G57" s="85" t="s">
+      <c r="G57" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="H57" s="39"/>
-      <c r="I57" s="39"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="27"/>
     </row>
     <row r="58" spans="1:11" ht="48.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="85"/>
-      <c r="B58" s="84"/>
-      <c r="C58" s="54" t="s">
+      <c r="A58" s="82"/>
+      <c r="B58" s="83"/>
+      <c r="C58" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D58" s="54" t="s">
+      <c r="D58" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="E58" s="84"/>
-      <c r="F58" s="85"/>
-      <c r="G58" s="85"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="39"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="82"/>
+      <c r="G58" s="82"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="35" t="s">
+      <c r="A59" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="35"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
-      <c r="G60" s="36"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="40"/>
+      <c r="B60" s="32">
+        <f>C35</f>
+        <v>7</v>
+      </c>
+      <c r="C60" s="32">
+        <f>C28</f>
+        <v>2</v>
+      </c>
+      <c r="D60" s="33">
+        <f>C60*C25</f>
+        <v>6</v>
+      </c>
+      <c r="E60" s="32">
+        <f>ROUND(D60*C8/C14,0)</f>
+        <v>7</v>
+      </c>
+      <c r="F60" s="32">
+        <f>C17*E60</f>
+        <v>12313</v>
+      </c>
+      <c r="G60" s="32">
+        <f>F60*G52</f>
+        <v>82992</v>
+      </c>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="40"/>
-      <c r="I61" s="40"/>
+      <c r="B61" s="32">
+        <f>C36</f>
+        <v>3</v>
+      </c>
+      <c r="C61" s="32">
+        <f>C29</f>
+        <v>4</v>
+      </c>
+      <c r="D61" s="33">
+        <f>C61*C25</f>
+        <v>12</v>
+      </c>
+      <c r="E61" s="32">
+        <f>ROUND(D61*C8/C14,0)</f>
+        <v>14</v>
+      </c>
+      <c r="F61" s="32">
+        <f>C17*E61</f>
+        <v>24626</v>
+      </c>
+      <c r="G61" s="32">
+        <f>F61*E52</f>
+        <v>137155.19999999998</v>
+      </c>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="33" t="s">
+      <c r="A62" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B62" s="32"/>
-      <c r="C62" s="46"/>
-      <c r="D62" s="46"/>
-      <c r="E62" s="46"/>
-      <c r="F62" s="46"/>
-      <c r="G62" s="46"/>
-      <c r="H62" s="40"/>
-      <c r="I62" s="40"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="37">
+        <f>SUM(C60:C61)</f>
+        <v>6</v>
+      </c>
+      <c r="D62" s="37">
+        <f>SUM(D60:D61)</f>
+        <v>18</v>
+      </c>
+      <c r="E62" s="37">
+        <f>SUM(E60:E61)</f>
+        <v>21</v>
+      </c>
+      <c r="F62" s="37">
+        <f>SUM(F60:F61)</f>
+        <v>36939</v>
+      </c>
+      <c r="G62" s="37">
+        <f>SUM(G60:G61)</f>
+        <v>220147.19999999998</v>
+      </c>
+      <c r="H62" s="28"/>
+      <c r="I62" s="28"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="35" t="s">
+      <c r="A63" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B63" s="35"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="43"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="49"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="39"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="27"/>
+      <c r="I63" s="27"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="33" t="s">
+      <c r="A64" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B64" s="36"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-      <c r="G64" s="45"/>
-      <c r="H64" s="40"/>
-      <c r="I64" s="41"/>
+      <c r="B64" s="32">
+        <f>C37</f>
+        <v>5</v>
+      </c>
+      <c r="C64" s="32">
+        <f>C30</f>
+        <v>1</v>
+      </c>
+      <c r="D64" s="33">
+        <f>C64*B25</f>
+        <v>2</v>
+      </c>
+      <c r="E64" s="32">
+        <f>ROUND(D64*C8/C14,0)</f>
+        <v>2</v>
+      </c>
+      <c r="F64" s="32">
+        <f>C17*E64</f>
+        <v>3518</v>
+      </c>
+      <c r="G64" s="36">
+        <f>F64*F52</f>
+        <v>21590.400000000001</v>
+      </c>
+      <c r="H64" s="28"/>
+      <c r="I64" s="34"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="33" t="s">
+      <c r="A65" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B65" s="36"/>
-      <c r="C65" s="36"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="36"/>
-      <c r="F65" s="36"/>
-      <c r="G65" s="45"/>
-      <c r="H65" s="40"/>
-      <c r="I65" s="40"/>
+      <c r="B65" s="32">
+        <f>C38</f>
+        <v>6</v>
+      </c>
+      <c r="C65" s="32">
+        <f>C31</f>
+        <v>2</v>
+      </c>
+      <c r="D65" s="33">
+        <f>C65*B25</f>
+        <v>4</v>
+      </c>
+      <c r="E65" s="32">
+        <f>ROUND(D65*C8/C14,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F65" s="32">
+        <f>C17*E65</f>
+        <v>8795</v>
+      </c>
+      <c r="G65" s="36">
+        <f>F65*H52</f>
+        <v>63336</v>
+      </c>
+      <c r="H65" s="28"/>
+      <c r="I65" s="28"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="33" t="s">
+      <c r="A66" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B66" s="48"/>
-      <c r="C66" s="47"/>
-      <c r="D66" s="47"/>
-      <c r="E66" s="47"/>
-      <c r="F66" s="47"/>
-      <c r="G66" s="47"/>
-      <c r="H66" s="40"/>
-      <c r="I66" s="40"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="38">
+        <f>SUM(C64:C65)</f>
+        <v>3</v>
+      </c>
+      <c r="D66" s="38">
+        <f>SUM(D64:D65)</f>
+        <v>6</v>
+      </c>
+      <c r="E66" s="38">
+        <f>SUM(E64:E65)</f>
+        <v>7</v>
+      </c>
+      <c r="F66" s="38">
+        <f>SUM(F64:F65)</f>
+        <v>12313</v>
+      </c>
+      <c r="G66" s="38">
+        <f>SUM(G64:G65)</f>
+        <v>84926.399999999994</v>
+      </c>
+      <c r="H66" s="28"/>
+      <c r="I66" s="28"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="35" t="s">
+      <c r="A67" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B67" s="35"/>
-      <c r="C67" s="35"/>
-      <c r="D67" s="43"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="44"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="39"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="27"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="33" t="s">
+      <c r="A68" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="45"/>
-      <c r="H68" s="40"/>
-      <c r="I68" s="40"/>
+      <c r="B68" s="32">
+        <f>C39</f>
+        <v>2</v>
+      </c>
+      <c r="C68" s="32">
+        <f>C32</f>
+        <v>2</v>
+      </c>
+      <c r="D68" s="33">
+        <f>C68*C25</f>
+        <v>6</v>
+      </c>
+      <c r="E68" s="32">
+        <f>ROUND(D68*C8/C14,0)</f>
+        <v>7</v>
+      </c>
+      <c r="F68" s="32">
+        <f>C17*E68</f>
+        <v>12313</v>
+      </c>
+      <c r="G68" s="36">
+        <f>F68*D52</f>
+        <v>58968</v>
+      </c>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="33" t="s">
+      <c r="A69" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="45"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="40"/>
+      <c r="B69" s="32">
+        <f>C40</f>
+        <v>2</v>
+      </c>
+      <c r="C69" s="32">
+        <f>C33</f>
+        <v>1</v>
+      </c>
+      <c r="D69" s="33">
+        <f>C69*C25</f>
+        <v>3</v>
+      </c>
+      <c r="E69" s="32">
+        <f>ROUND(D69*C8/C14,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F69" s="32">
+        <f>C17*E69</f>
+        <v>5277</v>
+      </c>
+      <c r="G69" s="36">
+        <f>F69*C52</f>
+        <v>21715.200000000001</v>
+      </c>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="33" t="s">
+      <c r="A70" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B70" s="32"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="40"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="37">
+        <f>SUM(C68:C69)</f>
+        <v>3</v>
+      </c>
+      <c r="D70" s="37">
+        <f>SUM(D68:D69)</f>
+        <v>9</v>
+      </c>
+      <c r="E70" s="37">
+        <f>SUM(E68:E69)</f>
+        <v>10</v>
+      </c>
+      <c r="F70" s="37">
+        <f>SUM(F68:F69)</f>
+        <v>17590</v>
+      </c>
+      <c r="G70" s="38">
+        <f>SUM(G68:G69)</f>
+        <v>80683.199999999997</v>
+      </c>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="33" t="s">
+      <c r="A71" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B71" s="32"/>
-      <c r="C71" s="50"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H72" s="42"/>
-      <c r="I72" s="42"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="40">
+        <f>SUM(C62,C66,C70)</f>
+        <v>12</v>
+      </c>
+      <c r="D71" s="40">
+        <f>SUM(D62,D66,D70)</f>
+        <v>33</v>
+      </c>
+      <c r="E71" s="40">
+        <f>SUM(E62,E66,E70)</f>
+        <v>38</v>
+      </c>
+      <c r="F71" s="40">
+        <f>SUM(F62,F66,F70)</f>
+        <v>66842</v>
+      </c>
+      <c r="G71" s="40">
+        <f>SUM(G62,G66,G70)</f>
+        <v>385756.8</v>
+      </c>
+      <c r="H71" s="28"/>
+      <c r="I71" s="28"/>
     </row>
     <row r="73" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="91" t="s">
+      <c r="A73" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="B73" s="91"/>
-      <c r="C73" s="91"/>
-      <c r="D73" s="91"/>
+      <c r="B73" s="73"/>
+      <c r="C73" s="73"/>
+      <c r="D73" s="73"/>
     </row>
     <row r="74" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="85" t="s">
+      <c r="A74" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="B74" s="88" t="s">
+      <c r="B74" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="C74" s="89"/>
-      <c r="D74" s="90"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-    </row>
-    <row r="75" spans="1:9" ht="48.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="85"/>
-      <c r="B75" s="5" t="s">
+      <c r="C74" s="79"/>
+      <c r="D74" s="80"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="27"/>
+    </row>
+    <row r="75" spans="1:9" ht="48.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="82"/>
+      <c r="B75" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E75" s="31"/>
-      <c r="F75" s="34"/>
-    </row>
-    <row r="76" spans="1:9" ht="18.3" x14ac:dyDescent="0.3">
-      <c r="A76" s="4" t="s">
+      <c r="E75" s="28"/>
+      <c r="F75" s="2"/>
+    </row>
+    <row r="76" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="31"/>
-      <c r="F76" s="3"/>
+      <c r="B76" s="8">
+        <f>G62</f>
+        <v>220147.19999999998</v>
+      </c>
+      <c r="C76" s="8">
+        <f>G66</f>
+        <v>84926.399999999994</v>
+      </c>
+      <c r="D76" s="8">
+        <f>G70</f>
+        <v>80683.199999999997</v>
+      </c>
+      <c r="E76" s="28"/>
+      <c r="F76" s="2"/>
     </row>
     <row r="77" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="31"/>
-      <c r="F77" s="3"/>
+      <c r="B77" s="8">
+        <f>B76*C24/100</f>
+        <v>121080.95999999998</v>
+      </c>
+      <c r="C77" s="8">
+        <f>C76*B24/100</f>
+        <v>42463.199999999997</v>
+      </c>
+      <c r="D77" s="8">
+        <f>D76*C24/100</f>
+        <v>44375.76</v>
+      </c>
+      <c r="E77" s="28"/>
+      <c r="F77" s="2"/>
     </row>
     <row r="78" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="86"/>
-      <c r="F78" s="87"/>
+      <c r="B78" s="8">
+        <f>B76/3*20/100</f>
+        <v>14676.48</v>
+      </c>
+      <c r="C78" s="8">
+        <f t="shared" ref="C78:D78" si="0">C76/3*20/100</f>
+        <v>5661.76</v>
+      </c>
+      <c r="D78" s="8">
+        <f t="shared" si="0"/>
+        <v>5378.88</v>
+      </c>
+      <c r="E78" s="84"/>
+      <c r="F78" s="85"/>
     </row>
     <row r="79" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B79" s="10"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="86"/>
-      <c r="F79" s="87"/>
-    </row>
-    <row r="80" spans="1:9" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="4" t="s">
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="84"/>
+      <c r="F79" s="85"/>
+    </row>
+    <row r="80" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B80" s="59"/>
-      <c r="C80" s="59"/>
-      <c r="D80" s="59"/>
-      <c r="E80" s="31"/>
-      <c r="F80" s="3"/>
-    </row>
-    <row r="81" spans="1:7" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="4" t="s">
+      <c r="B80" s="49">
+        <f>SUM(B76:B79)</f>
+        <v>355904.63999999996</v>
+      </c>
+      <c r="C80" s="49">
+        <f t="shared" ref="C80:D80" si="1">SUM(C76:C79)</f>
+        <v>133051.35999999999</v>
+      </c>
+      <c r="D80" s="49">
+        <f t="shared" si="1"/>
+        <v>130437.84</v>
+      </c>
+      <c r="E80" s="28"/>
+      <c r="F80" s="2"/>
+    </row>
+    <row r="81" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B81" s="62"/>
-      <c r="C81" s="62"/>
-      <c r="D81" s="62"/>
-      <c r="E81" s="31"/>
-      <c r="F81" s="3"/>
-    </row>
-    <row r="82" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="4" t="s">
+      <c r="B81" s="52">
+        <f>(C9-(C11+C12))/C14*100</f>
+        <v>13.122171945701359</v>
+      </c>
+      <c r="C81" s="52">
+        <f>(C9-(C11+C12))/C14*100</f>
+        <v>13.122171945701359</v>
+      </c>
+      <c r="D81" s="52">
+        <f>(C9-(C11+C12))/C14*100</f>
+        <v>13.122171945701359</v>
+      </c>
+      <c r="E81" s="28"/>
+      <c r="F81" s="2"/>
+    </row>
+    <row r="82" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B82" s="59"/>
-      <c r="C82" s="59"/>
-      <c r="D82" s="59"/>
-      <c r="E82" s="31"/>
-      <c r="F82" s="3"/>
+      <c r="B82" s="49">
+        <f>B80*B81/100</f>
+        <v>46702.418823529406</v>
+      </c>
+      <c r="C82" s="49">
+        <f>C80*C81/100</f>
+        <v>17459.228235294118</v>
+      </c>
+      <c r="D82" s="49">
+        <f>D80*D81/100</f>
+        <v>17116.277647058825</v>
+      </c>
+      <c r="E82" s="28"/>
+      <c r="F82" s="2"/>
     </row>
     <row r="83" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A83" s="58" t="s">
+      <c r="A83" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="B83" s="78"/>
-      <c r="C83" s="78"/>
-      <c r="D83" s="78"/>
-      <c r="E83" s="30"/>
-      <c r="F83" s="30"/>
+      <c r="B83" s="67">
+        <f>SUM(B80,B82)</f>
+        <v>402607.05882352934</v>
+      </c>
+      <c r="C83" s="67">
+        <f t="shared" ref="C83:D83" si="2">SUM(C80,C82)</f>
+        <v>150510.5882352941</v>
+      </c>
+      <c r="D83" s="67">
+        <f t="shared" si="2"/>
+        <v>147554.11764705883</v>
+      </c>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
     </row>
     <row r="85" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="92" t="s">
+      <c r="A85" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="B85" s="92"/>
-      <c r="C85" s="92"/>
-      <c r="D85" s="92"/>
-      <c r="E85" s="92"/>
-      <c r="F85" s="92"/>
-      <c r="G85" s="92"/>
-    </row>
-    <row r="86" spans="1:7" ht="26.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="s">
+      <c r="B85" s="74"/>
+      <c r="C85" s="74"/>
+      <c r="D85" s="74"/>
+      <c r="E85" s="74"/>
+      <c r="F85" s="74"/>
+      <c r="G85" s="74"/>
+    </row>
+    <row r="86" spans="1:7" ht="26.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B86" s="84" t="s">
+      <c r="B86" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="85" t="s">
+      <c r="C86" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="D86" s="88" t="s">
+      <c r="D86" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="E86" s="89"/>
-      <c r="F86" s="89"/>
-      <c r="G86" s="90"/>
-    </row>
-    <row r="87" spans="1:7" ht="53.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5"/>
-      <c r="B87" s="84"/>
-      <c r="C87" s="85"/>
-      <c r="D87" s="7" t="s">
+      <c r="E86" s="79"/>
+      <c r="F86" s="79"/>
+      <c r="G86" s="80"/>
+    </row>
+    <row r="87" spans="1:7" ht="53.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="4"/>
+      <c r="B87" s="83"/>
+      <c r="C87" s="82"/>
+      <c r="D87" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="F87" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G87" s="7" t="s">
+      <c r="G87" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A88" s="61" t="s">
+      <c r="A88" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="10"/>
+      <c r="B88" s="8">
+        <f>C42</f>
+        <v>2</v>
+      </c>
+      <c r="C88" s="8">
+        <f>C46</f>
+        <v>3100</v>
+      </c>
+      <c r="D88" s="6">
+        <f>C88*12*B88</f>
+        <v>74400</v>
+      </c>
+      <c r="E88" s="8">
+        <f>D88*50/100</f>
+        <v>37200</v>
+      </c>
+      <c r="F88" s="8">
+        <f>B81*D88/100</f>
+        <v>9762.8959276018104</v>
+      </c>
+      <c r="G88" s="8">
+        <f>SUM(D88:F88)</f>
+        <v>121362.89592760181</v>
+      </c>
     </row>
     <row r="89" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="10"/>
+      <c r="B89" s="8">
+        <f t="shared" ref="B89:B90" si="3">C43</f>
+        <v>2</v>
+      </c>
+      <c r="C89" s="8">
+        <f t="shared" ref="C89:C90" si="4">C47</f>
+        <v>2800</v>
+      </c>
+      <c r="D89" s="6">
+        <f>C89*12*B89</f>
+        <v>67200</v>
+      </c>
+      <c r="E89" s="8">
+        <f t="shared" ref="E89:E90" si="5">D89*50/100</f>
+        <v>33600</v>
+      </c>
+      <c r="F89" s="8">
+        <f>B81*D89/100</f>
+        <v>8818.0995475113141</v>
+      </c>
+      <c r="G89" s="8">
+        <f t="shared" ref="G89:G90" si="6">SUM(D89:F89)</f>
+        <v>109618.09954751132</v>
+      </c>
     </row>
     <row r="90" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B90" s="10"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
+      <c r="B90" s="8">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="C90" s="8">
+        <f t="shared" si="4"/>
+        <v>2580</v>
+      </c>
+      <c r="D90" s="6">
+        <f>C90*12*B90</f>
+        <v>92880</v>
+      </c>
+      <c r="E90" s="8">
+        <f t="shared" si="5"/>
+        <v>46440</v>
+      </c>
+      <c r="F90" s="8">
+        <f>B81*D90/100</f>
+        <v>12187.873303167422</v>
+      </c>
+      <c r="G90" s="8">
+        <f t="shared" si="6"/>
+        <v>151507.87330316743</v>
+      </c>
     </row>
     <row r="91" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B91" s="59"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="59"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="59"/>
-      <c r="G91" s="59"/>
+      <c r="B91" s="49">
+        <f>SUM(B88:B90)</f>
+        <v>7</v>
+      </c>
+      <c r="C91" s="14"/>
+      <c r="D91" s="49">
+        <f>SUM(D88:D90)</f>
+        <v>234480</v>
+      </c>
+      <c r="E91" s="49">
+        <f>SUM(E88:E90)</f>
+        <v>117240</v>
+      </c>
+      <c r="F91" s="49">
+        <f>SUM(F88:F90)</f>
+        <v>30768.868778280543</v>
+      </c>
+      <c r="G91" s="49">
+        <f>SUM(G88:G90)</f>
+        <v>382488.86877828056</v>
+      </c>
     </row>
     <row r="93" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="63" t="s">
+      <c r="A93" s="53" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A94" s="64" t="s">
+    <row r="94" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A95" s="64" t="s">
+      <c r="B94" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B95" s="65"/>
-    </row>
-    <row r="96" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A96" s="64" t="s">
+      <c r="B95" s="54">
+        <f>SUM(G91,B83,C83,D83)</f>
+        <v>1083160.6334841629</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B96" s="65"/>
-    </row>
-    <row r="97" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A97" s="64" t="s">
+      <c r="B96" s="54">
+        <f>SUM(B91,E71)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B97" s="66"/>
-    </row>
-    <row r="98" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A98" s="64" t="s">
+      <c r="B97" s="55">
+        <f>B95/B96</f>
+        <v>24070.236299648062</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B98" s="66"/>
-    </row>
-    <row r="99" spans="1:2" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="64" t="s">
+      <c r="B98" s="55">
+        <f>B97/12</f>
+        <v>2005.8530249706719</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="66"/>
-    </row>
-    <row r="100" spans="1:2" ht="29.55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="64" t="s">
+      <c r="B99" s="55">
+        <f>C26/B96</f>
+        <v>354.66666666666669</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B100" s="66"/>
-    </row>
-    <row r="101" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A101" s="64" t="s">
+      <c r="B100" s="55">
+        <f>B101*8</f>
+        <v>1.613037710820542</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B101" s="66"/>
+      <c r="B101" s="55">
+        <f>C26/B96/C17</f>
+        <v>0.20162971385256775</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="D86:G86"/>
+    <mergeCell ref="B74:D74"/>
     <mergeCell ref="A73:D73"/>
     <mergeCell ref="A85:G85"/>
     <mergeCell ref="A3:K3"/>
@@ -3436,13 +3780,6 @@
     <mergeCell ref="E57:E58"/>
     <mergeCell ref="F57:F58"/>
     <mergeCell ref="G57:G58"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="D86:G86"/>
-    <mergeCell ref="B74:D74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -3452,115 +3789,115 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="110.296875" customWidth="1"/>
+    <col min="1" max="1" width="110.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.3" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="58" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="18.3" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
+    <row r="2" spans="1:1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="63" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="46.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="70" t="s">
+    <row r="3" spans="1:1" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="59" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="71"/>
-    </row>
-    <row r="5" spans="1:1" ht="62.35" x14ac:dyDescent="0.3">
-      <c r="A5" s="72" t="s">
+      <c r="A4" s="60"/>
+    </row>
+    <row r="5" spans="1:1" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="61" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="71"/>
+      <c r="A6" s="60"/>
     </row>
     <row r="7" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="64" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
+      <c r="A8" s="60"/>
     </row>
     <row r="9" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="65" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="60" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="59" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
-    </row>
-    <row r="13" spans="1:1" ht="124.7" x14ac:dyDescent="0.3">
-      <c r="A13" s="77" t="s">
+      <c r="A12" s="60"/>
+    </row>
+    <row r="13" spans="1:1" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="66" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="66.650000000000006" x14ac:dyDescent="0.3">
-      <c r="A14" s="80" t="s">
+    <row r="14" spans="1:1" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="69" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="17.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="57" t="s">
+    <row r="15" spans="1:1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A15" s="47" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="109.1" x14ac:dyDescent="0.3">
-      <c r="A16" s="79" t="s">
+    <row r="16" spans="1:1" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="68" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="47" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="47" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="77.95" x14ac:dyDescent="0.3">
-      <c r="A19" s="81" t="s">
+    <row r="19" spans="1:1" ht="78" x14ac:dyDescent="0.3">
+      <c r="A19" s="70" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="46.75" x14ac:dyDescent="0.3">
-      <c r="A21" s="73" t="s">
+    <row r="21" spans="1:1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="62" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="17.75" x14ac:dyDescent="0.45">
-      <c r="A22" s="83" t="s">
+    <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A22" s="72" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="17.75" x14ac:dyDescent="0.45">
-      <c r="A23" s="83" t="s">
+    <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A23" s="72" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="33.35" x14ac:dyDescent="0.3">
-      <c r="A24" s="82" t="s">
+    <row r="24" spans="1:1" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="71" t="s">
         <v>105</v>
       </c>
     </row>

--- a/3k2s/Экономика IT-компании/Лабораторная работа 2_ФОТ_с.xlsx
+++ b/3k2s/Экономика IT-компании/Лабораторная работа 2_ФОТ_с.xlsx
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="113">
   <si>
     <t>Показатель</t>
   </si>
@@ -636,6 +638,9 @@
   </si>
   <si>
     <t>5. Эффективный фонд времени в днях (п.3-п.4)</t>
+  </si>
+  <si>
+    <t>Как высчитать сдельную оплату труда</t>
   </si>
 </sst>
 </file>
@@ -945,7 +950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1199,6 +1204,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1480,14 +1488,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="59.5546875" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="11.33203125" customWidth="1"/>
     <col min="8" max="8" width="9.6640625" customWidth="1"/>
@@ -1531,7 +1539,7 @@
       <c r="J4" s="79"/>
       <c r="K4" s="80"/>
     </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="56">
         <v>1</v>
@@ -1634,7 +1642,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
@@ -1740,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>7</v>
       </c>
@@ -1828,7 +1836,7 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="29.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
@@ -1946,7 +1954,7 @@
       <c r="J21" s="79"/>
       <c r="K21" s="80"/>
     </row>
-    <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="56">
         <v>1</v>
@@ -3045,8 +3053,8 @@
         <v>12313</v>
       </c>
       <c r="G60" s="32">
-        <f>F60*G52</f>
-        <v>82992</v>
+        <f>F60*H52</f>
+        <v>88670.399999999994</v>
       </c>
       <c r="H60" s="28"/>
       <c r="I60" s="28"/>
@@ -3076,8 +3084,8 @@
         <v>24626</v>
       </c>
       <c r="G61" s="32">
-        <f>F61*E52</f>
-        <v>137155.19999999998</v>
+        <f>F61*D52</f>
+        <v>117936</v>
       </c>
       <c r="H61" s="28"/>
       <c r="I61" s="28"/>
@@ -3105,7 +3113,7 @@
       </c>
       <c r="G62" s="37">
         <f>SUM(G60:G61)</f>
-        <v>220147.19999999998</v>
+        <v>206606.4</v>
       </c>
       <c r="H62" s="28"/>
       <c r="I62" s="28"/>
@@ -3136,20 +3144,19 @@
         <v>1</v>
       </c>
       <c r="D64" s="33">
-        <f>C64*B25</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" s="32">
         <f>ROUND(D64*C8/C14,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="32">
         <f>C17*E64</f>
-        <v>3518</v>
+        <v>5277</v>
       </c>
       <c r="G64" s="36">
         <f>F64*F52</f>
-        <v>21590.400000000001</v>
+        <v>32385.600000000002</v>
       </c>
       <c r="H64" s="28"/>
       <c r="I64" s="34"/>
@@ -3167,20 +3174,19 @@
         <v>2</v>
       </c>
       <c r="D65" s="33">
-        <f>C65*B25</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E65" s="32">
         <f>ROUND(D65*C8/C14,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F65" s="32">
         <f>C17*E65</f>
-        <v>8795</v>
+        <v>12313</v>
       </c>
       <c r="G65" s="36">
-        <f>F65*H52</f>
-        <v>63336</v>
+        <f>F65*G52</f>
+        <v>82992</v>
       </c>
       <c r="H65" s="28"/>
       <c r="I65" s="28"/>
@@ -3196,19 +3202,19 @@
       </c>
       <c r="D66" s="38">
         <f>SUM(D64:D65)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E66" s="38">
         <f>SUM(E64:E65)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F66" s="38">
         <f>SUM(F64:F65)</f>
-        <v>12313</v>
+        <v>17590</v>
       </c>
       <c r="G66" s="38">
         <f>SUM(G64:G65)</f>
-        <v>84926.399999999994</v>
+        <v>115377.60000000001</v>
       </c>
       <c r="H66" s="28"/>
       <c r="I66" s="28"/>
@@ -3251,8 +3257,8 @@
         <v>12313</v>
       </c>
       <c r="G68" s="36">
-        <f>F68*D52</f>
-        <v>58968</v>
+        <f>F68*C52</f>
+        <v>50668.799999999996</v>
       </c>
       <c r="H68" s="28"/>
       <c r="I68" s="28"/>
@@ -3311,7 +3317,7 @@
       </c>
       <c r="G70" s="38">
         <f>SUM(G68:G69)</f>
-        <v>80683.199999999997</v>
+        <v>72384</v>
       </c>
       <c r="H70" s="28"/>
       <c r="I70" s="28"/>
@@ -3327,19 +3333,19 @@
       </c>
       <c r="D71" s="40">
         <f>SUM(D62,D66,D70)</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E71" s="40">
         <f>SUM(E62,E66,E70)</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F71" s="40">
         <f>SUM(F62,F66,F70)</f>
-        <v>66842</v>
+        <v>72119</v>
       </c>
       <c r="G71" s="40">
         <f>SUM(G62,G66,G70)</f>
-        <v>385756.8</v>
+        <v>394368</v>
       </c>
       <c r="H71" s="28"/>
       <c r="I71" s="28"/>
@@ -3352,7 +3358,7 @@
       <c r="C73" s="73"/>
       <c r="D73" s="73"/>
     </row>
-    <row r="74" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="82" t="s">
         <v>60</v>
       </c>
@@ -3384,34 +3390,34 @@
       </c>
       <c r="B76" s="8">
         <f>G62</f>
-        <v>220147.19999999998</v>
+        <v>206606.4</v>
       </c>
       <c r="C76" s="8">
         <f>G66</f>
-        <v>84926.399999999994</v>
+        <v>115377.60000000001</v>
       </c>
       <c r="D76" s="8">
         <f>G70</f>
-        <v>80683.199999999997</v>
+        <v>72384</v>
       </c>
       <c r="E76" s="28"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B77" s="8">
         <f>B76*C24/100</f>
-        <v>121080.95999999998</v>
+        <v>113633.52</v>
       </c>
       <c r="C77" s="8">
         <f>C76*B24/100</f>
-        <v>42463.199999999997</v>
+        <v>57688.800000000003</v>
       </c>
       <c r="D77" s="8">
         <f>D76*C24/100</f>
-        <v>44375.76</v>
+        <v>39811.199999999997</v>
       </c>
       <c r="E77" s="28"/>
       <c r="F77" s="2"/>
@@ -3422,15 +3428,15 @@
       </c>
       <c r="B78" s="8">
         <f>B76/3*20/100</f>
-        <v>14676.48</v>
+        <v>13773.76</v>
       </c>
       <c r="C78" s="8">
         <f t="shared" ref="C78:D78" si="0">C76/3*20/100</f>
-        <v>5661.76</v>
+        <v>7691.8400000000011</v>
       </c>
       <c r="D78" s="8">
         <f t="shared" si="0"/>
-        <v>5378.88</v>
+        <v>4825.6000000000004</v>
       </c>
       <c r="E78" s="84"/>
       <c r="F78" s="85"/>
@@ -3439,9 +3445,18 @@
       <c r="A79" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
+      <c r="B79" s="8">
+        <f>B76/3*40/100</f>
+        <v>27547.52</v>
+      </c>
+      <c r="C79" s="8">
+        <f>C76/3*(40/100)</f>
+        <v>15383.680000000002</v>
+      </c>
+      <c r="D79" s="8">
+        <f>D76/3*(40/100)</f>
+        <v>9651.2000000000007</v>
+      </c>
       <c r="E79" s="84"/>
       <c r="F79" s="85"/>
     </row>
@@ -3451,15 +3466,15 @@
       </c>
       <c r="B80" s="49">
         <f>SUM(B76:B79)</f>
-        <v>355904.63999999996</v>
+        <v>361561.2</v>
       </c>
       <c r="C80" s="49">
         <f t="shared" ref="C80:D80" si="1">SUM(C76:C79)</f>
-        <v>133051.35999999999</v>
+        <v>196141.92</v>
       </c>
       <c r="D80" s="49">
         <f t="shared" si="1"/>
-        <v>130437.84</v>
+        <v>126672</v>
       </c>
       <c r="E80" s="28"/>
       <c r="F80" s="2"/>
@@ -3489,15 +3504,15 @@
       </c>
       <c r="B82" s="49">
         <f>B80*B81/100</f>
-        <v>46702.418823529406</v>
+        <v>47444.682352941185</v>
       </c>
       <c r="C82" s="49">
         <f>C80*C81/100</f>
-        <v>17459.228235294118</v>
+        <v>25738.080000000005</v>
       </c>
       <c r="D82" s="49">
         <f>D80*D81/100</f>
-        <v>17116.277647058825</v>
+        <v>16622.117647058825</v>
       </c>
       <c r="E82" s="28"/>
       <c r="F82" s="2"/>
@@ -3508,15 +3523,15 @@
       </c>
       <c r="B83" s="67">
         <f>SUM(B80,B82)</f>
-        <v>402607.05882352934</v>
+        <v>409005.8823529412</v>
       </c>
       <c r="C83" s="67">
         <f t="shared" ref="C83:D83" si="2">SUM(C80,C82)</f>
-        <v>150510.5882352941</v>
+        <v>221880.00000000003</v>
       </c>
       <c r="D83" s="67">
         <f t="shared" si="2"/>
-        <v>147554.11764705883</v>
+        <v>143294.11764705883</v>
       </c>
       <c r="E83" s="27"/>
       <c r="F83" s="27"/>
@@ -3583,8 +3598,8 @@
         <v>74400</v>
       </c>
       <c r="E88" s="8">
-        <f>D88*50/100</f>
-        <v>37200</v>
+        <f>D88*C24/100</f>
+        <v>40920</v>
       </c>
       <c r="F88" s="8">
         <f>B81*D88/100</f>
@@ -3592,7 +3607,7 @@
       </c>
       <c r="G88" s="8">
         <f>SUM(D88:F88)</f>
-        <v>121362.89592760181</v>
+        <v>125082.89592760181</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -3612,16 +3627,16 @@
         <v>67200</v>
       </c>
       <c r="E89" s="8">
-        <f t="shared" ref="E89:E90" si="5">D89*50/100</f>
-        <v>33600</v>
+        <f>D89*C24/100</f>
+        <v>36960</v>
       </c>
       <c r="F89" s="8">
         <f>B81*D89/100</f>
         <v>8818.0995475113141</v>
       </c>
       <c r="G89" s="8">
-        <f t="shared" ref="G89:G90" si="6">SUM(D89:F89)</f>
-        <v>109618.09954751132</v>
+        <f t="shared" ref="G89:G90" si="5">SUM(D89:F89)</f>
+        <v>112978.09954751132</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -3641,16 +3656,16 @@
         <v>92880</v>
       </c>
       <c r="E90" s="8">
-        <f t="shared" si="5"/>
-        <v>46440</v>
+        <f>D90*C24/100</f>
+        <v>51084</v>
       </c>
       <c r="F90" s="8">
         <f>B81*D90/100</f>
         <v>12187.873303167422</v>
       </c>
       <c r="G90" s="8">
-        <f t="shared" si="6"/>
-        <v>151507.87330316743</v>
+        <f t="shared" si="5"/>
+        <v>156151.87330316743</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -3668,7 +3683,7 @@
       </c>
       <c r="E91" s="49">
         <f>SUM(E88:E90)</f>
-        <v>117240</v>
+        <v>128964</v>
       </c>
       <c r="F91" s="49">
         <f>SUM(F88:F90)</f>
@@ -3676,7 +3691,7 @@
       </c>
       <c r="G91" s="49">
         <f>SUM(G88:G90)</f>
-        <v>382488.86877828056</v>
+        <v>394212.86877828056</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -3698,7 +3713,7 @@
       </c>
       <c r="B95" s="54">
         <f>SUM(G91,B83,C83,D83)</f>
-        <v>1083160.6334841629</v>
+        <v>1168392.8687782807</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -3707,7 +3722,7 @@
       </c>
       <c r="B96" s="54">
         <f>SUM(B91,E71)</f>
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -3716,7 +3731,7 @@
       </c>
       <c r="B97" s="55">
         <f>B95/B96</f>
-        <v>24070.236299648062</v>
+        <v>24341.518099547513</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -3725,7 +3740,7 @@
       </c>
       <c r="B98" s="55">
         <f>B97/12</f>
-        <v>2005.8530249706719</v>
+        <v>2028.4598416289593</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3734,16 +3749,16 @@
       </c>
       <c r="B99" s="55">
         <f>C26/B96</f>
-        <v>354.66666666666669</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
+        <v>332.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="29.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B100" s="55">
         <f>B101*8</f>
-        <v>1.613037710820542</v>
+        <v>1.5122228538942581</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -3752,11 +3767,157 @@
       </c>
       <c r="B101" s="55">
         <f>C26/B96/C17</f>
-        <v>0.20162971385256775</v>
-      </c>
+        <v>0.18902785673678227</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" s="86" t="s">
+        <v>112</v>
+      </c>
+      <c r="B118" s="86"/>
+      <c r="C118" s="86"/>
+      <c r="D118" s="86"/>
+      <c r="E118" s="86"/>
+      <c r="F118" s="86"/>
+      <c r="G118" s="86"/>
+      <c r="H118" s="86"/>
+      <c r="I118" s="86"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="86"/>
+      <c r="B119" s="86"/>
+      <c r="C119" s="86"/>
+      <c r="D119" s="86"/>
+      <c r="E119" s="86"/>
+      <c r="F119" s="86"/>
+      <c r="G119" s="86"/>
+      <c r="H119" s="86"/>
+      <c r="I119" s="86"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" s="86"/>
+      <c r="B120" s="86"/>
+      <c r="C120" s="86"/>
+      <c r="D120" s="86"/>
+      <c r="E120" s="86"/>
+      <c r="F120" s="86"/>
+      <c r="G120" s="86"/>
+      <c r="H120" s="86"/>
+      <c r="I120" s="86"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" s="86"/>
+      <c r="B121" s="86"/>
+      <c r="C121" s="86"/>
+      <c r="D121" s="86"/>
+      <c r="E121" s="86"/>
+      <c r="F121" s="86"/>
+      <c r="G121" s="86"/>
+      <c r="H121" s="86"/>
+      <c r="I121" s="86"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" s="86"/>
+      <c r="B122" s="86"/>
+      <c r="C122" s="86"/>
+      <c r="D122" s="86"/>
+      <c r="E122" s="86"/>
+      <c r="F122" s="86"/>
+      <c r="G122" s="86"/>
+      <c r="H122" s="86"/>
+      <c r="I122" s="86"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="86"/>
+      <c r="B123" s="86"/>
+      <c r="C123" s="86"/>
+      <c r="D123" s="86"/>
+      <c r="E123" s="86"/>
+      <c r="F123" s="86"/>
+      <c r="G123" s="86"/>
+      <c r="H123" s="86"/>
+      <c r="I123" s="86"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" s="86"/>
+      <c r="B124" s="86"/>
+      <c r="C124" s="86"/>
+      <c r="D124" s="86"/>
+      <c r="E124" s="86"/>
+      <c r="F124" s="86"/>
+      <c r="G124" s="86"/>
+      <c r="H124" s="86"/>
+      <c r="I124" s="86"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" s="86"/>
+      <c r="B125" s="86"/>
+      <c r="C125" s="86"/>
+      <c r="D125" s="86"/>
+      <c r="E125" s="86"/>
+      <c r="F125" s="86"/>
+      <c r="G125" s="86"/>
+      <c r="H125" s="86"/>
+      <c r="I125" s="86"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" s="86"/>
+      <c r="B126" s="86"/>
+      <c r="C126" s="86"/>
+      <c r="D126" s="86"/>
+      <c r="E126" s="86"/>
+      <c r="F126" s="86"/>
+      <c r="G126" s="86"/>
+      <c r="H126" s="86"/>
+      <c r="I126" s="86"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="86"/>
+      <c r="B127" s="86"/>
+      <c r="C127" s="86"/>
+      <c r="D127" s="86"/>
+      <c r="E127" s="86"/>
+      <c r="F127" s="86"/>
+      <c r="G127" s="86"/>
+      <c r="H127" s="86"/>
+      <c r="I127" s="86"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="86"/>
+      <c r="B128" s="86"/>
+      <c r="C128" s="86"/>
+      <c r="D128" s="86"/>
+      <c r="E128" s="86"/>
+      <c r="F128" s="86"/>
+      <c r="G128" s="86"/>
+      <c r="H128" s="86"/>
+      <c r="I128" s="86"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" s="86"/>
+      <c r="B129" s="86"/>
+      <c r="C129" s="86"/>
+      <c r="D129" s="86"/>
+      <c r="E129" s="86"/>
+      <c r="F129" s="86"/>
+      <c r="G129" s="86"/>
+      <c r="H129" s="86"/>
+      <c r="I129" s="86"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" s="86"/>
+      <c r="B130" s="86"/>
+      <c r="C130" s="86"/>
+      <c r="D130" s="86"/>
+      <c r="E130" s="86"/>
+      <c r="F130" s="86"/>
+      <c r="G130" s="86"/>
+      <c r="H130" s="86"/>
+      <c r="I130" s="86"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
+    <mergeCell ref="A118:I130"/>
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:C87"/>
     <mergeCell ref="E78:E79"/>

--- a/3k2s/Экономика IT-компании/Лабораторная работа 2_ФОТ_с.xlsx
+++ b/3k2s/Экономика IT-компании/Лабораторная работа 2_ФОТ_с.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Задание исх данные, решение 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="114">
   <si>
     <t>Показатель</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Разряд</t>
-  </si>
-  <si>
-    <t>Часовая тарифная ставка, руб.</t>
   </si>
   <si>
     <t>Тарифный коэффициент</t>
@@ -641,6 +638,12 @@
   </si>
   <si>
     <t>Как высчитать сдельную оплату труда</t>
+  </si>
+  <si>
+    <t>Часовая тарифная ставка, руб/час.</t>
+  </si>
+  <si>
+    <t>теория: как расчитать простую сдельную оплату; как расчитать сдельную премиальную оплату</t>
   </si>
 </sst>
 </file>
@@ -816,7 +819,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,6 +841,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -950,7 +959,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1166,6 +1175,30 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1181,32 +1214,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1504,23 +1528,23 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="77"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="85"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1544,7 +1568,7 @@
       <c r="B5" s="56">
         <v>1</v>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="87">
         <v>2</v>
       </c>
       <c r="D5" s="57">
@@ -1579,7 +1603,7 @@
       <c r="B6" s="7">
         <v>365</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="88">
         <v>365</v>
       </c>
       <c r="D6" s="7">
@@ -1614,7 +1638,7 @@
       <c r="B7" s="7">
         <v>113</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="88">
         <v>112</v>
       </c>
       <c r="D7" s="7">
@@ -1647,7 +1671,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="8"/>
-      <c r="C8" s="8">
+      <c r="C8" s="88">
         <f>C6-C7</f>
         <v>253</v>
       </c>
@@ -1662,10 +1686,10 @@
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="8"/>
-      <c r="C9" s="8">
+      <c r="C9" s="88">
         <f>SUM(C10:C13)</f>
         <v>32</v>
       </c>
@@ -1685,7 +1709,7 @@
       <c r="B10" s="7">
         <v>26</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="89">
         <v>28</v>
       </c>
       <c r="D10" s="9">
@@ -1720,7 +1744,7 @@
       <c r="B11" s="7">
         <v>3</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="89">
         <v>1</v>
       </c>
       <c r="D11" s="9">
@@ -1755,7 +1779,7 @@
       <c r="B12" s="7">
         <v>3</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="89">
         <v>2</v>
       </c>
       <c r="D12" s="9">
@@ -1790,7 +1814,7 @@
       <c r="B13" s="7">
         <v>2</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="88">
         <v>1</v>
       </c>
       <c r="D13" s="7">
@@ -1820,10 +1844,10 @@
     </row>
     <row r="14" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B14" s="8"/>
-      <c r="C14" s="8">
+      <c r="C14" s="88">
         <f>C8-C9</f>
         <v>221</v>
       </c>
@@ -1838,10 +1862,10 @@
     </row>
     <row r="15" spans="1:11" ht="29.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="8"/>
-      <c r="C15" s="8">
+      <c r="C15" s="88">
         <f>C14*8</f>
         <v>1768</v>
       </c>
@@ -1856,12 +1880,12 @@
     </row>
     <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" s="7">
         <v>10</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="88">
         <v>9</v>
       </c>
       <c r="D16" s="7">
@@ -1894,7 +1918,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="8"/>
-      <c r="C17" s="8">
+      <c r="C17" s="88">
         <f>C15-C16</f>
         <v>1759</v>
       </c>
@@ -1909,10 +1933,10 @@
     </row>
     <row r="18" spans="1:11" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B18" s="8"/>
-      <c r="C18" s="8">
+      <c r="C18" s="88">
         <f>C17/12</f>
         <v>146.58333333333334</v>
       </c>
@@ -1926,16 +1950,16 @@
       <c r="K18" s="8"/>
     </row>
     <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="81" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="81"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
+      <c r="A20" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
     </row>
     <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
@@ -1959,7 +1983,7 @@
       <c r="B22" s="56">
         <v>1</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="87">
         <v>2</v>
       </c>
       <c r="D22" s="57">
@@ -1989,12 +2013,12 @@
     </row>
     <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B23" s="7">
         <v>600</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="88">
         <v>520</v>
       </c>
       <c r="D23" s="7">
@@ -2024,12 +2048,12 @@
     </row>
     <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="7">
         <v>50</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="88">
         <v>55</v>
       </c>
       <c r="D24" s="7">
@@ -2059,12 +2083,12 @@
     </row>
     <row r="25" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="7">
         <v>2</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="88">
         <v>3</v>
       </c>
       <c r="D25" s="7">
@@ -2094,12 +2118,12 @@
     </row>
     <row r="26" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26" s="7">
         <v>13380</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="88">
         <v>15960</v>
       </c>
       <c r="D26" s="7">
@@ -2129,10 +2153,10 @@
     </row>
     <row r="27" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B27" s="16"/>
-      <c r="C27" s="17"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
@@ -2144,12 +2168,12 @@
     </row>
     <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B28" s="20">
         <v>1</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="88">
         <v>2</v>
       </c>
       <c r="D28" s="21">
@@ -2179,12 +2203,12 @@
     </row>
     <row r="29" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" s="20">
         <v>5</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="88">
         <v>4</v>
       </c>
       <c r="D29" s="21">
@@ -2214,12 +2238,12 @@
     </row>
     <row r="30" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B30" s="20">
         <v>1</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="88">
         <v>1</v>
       </c>
       <c r="D30" s="21">
@@ -2249,12 +2273,12 @@
     </row>
     <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" s="20">
         <v>1</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C31" s="88">
         <v>2</v>
       </c>
       <c r="D31" s="21">
@@ -2284,12 +2308,12 @@
     </row>
     <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" s="20">
         <v>2</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="88">
         <v>2</v>
       </c>
       <c r="D32" s="21">
@@ -2319,12 +2343,12 @@
     </row>
     <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" s="20">
         <v>3</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="88">
         <v>1</v>
       </c>
       <c r="D33" s="21">
@@ -2354,10 +2378,10 @@
     </row>
     <row r="34" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B34" s="23"/>
-      <c r="C34" s="24"/>
+      <c r="C34" s="91"/>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
       <c r="F34" s="24"/>
@@ -2369,12 +2393,12 @@
     </row>
     <row r="35" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" s="23">
         <v>6</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="91">
         <v>7</v>
       </c>
       <c r="D35" s="24">
@@ -2404,12 +2428,12 @@
     </row>
     <row r="36" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" s="23">
         <v>4</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="91">
         <v>3</v>
       </c>
       <c r="D36" s="24">
@@ -2439,12 +2463,12 @@
     </row>
     <row r="37" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" s="23">
         <v>5</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="91">
         <v>5</v>
       </c>
       <c r="D37" s="24">
@@ -2474,12 +2498,12 @@
     </row>
     <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="23">
         <v>7</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="91">
         <v>6</v>
       </c>
       <c r="D38" s="24">
@@ -2509,12 +2533,12 @@
     </row>
     <row r="39" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" s="23">
         <v>3</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="91">
         <v>2</v>
       </c>
       <c r="D39" s="24">
@@ -2544,12 +2568,12 @@
     </row>
     <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B40" s="23">
         <v>2</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="91">
         <v>2</v>
       </c>
       <c r="D40" s="24">
@@ -2579,10 +2603,10 @@
     </row>
     <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B41" s="20"/>
-      <c r="C41" s="21"/>
+      <c r="C41" s="88"/>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
@@ -2594,12 +2618,12 @@
     </row>
     <row r="42" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B42" s="20">
         <v>1</v>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="88">
         <v>2</v>
       </c>
       <c r="D42" s="21">
@@ -2629,12 +2653,12 @@
     </row>
     <row r="43" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" s="20">
         <v>1</v>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="88">
         <v>2</v>
       </c>
       <c r="D43" s="21">
@@ -2664,12 +2688,12 @@
     </row>
     <row r="44" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B44" s="20">
         <v>2</v>
       </c>
-      <c r="C44" s="21">
+      <c r="C44" s="88">
         <v>3</v>
       </c>
       <c r="D44" s="21">
@@ -2700,10 +2724,10 @@
     </row>
     <row r="45" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="20"/>
-      <c r="C45" s="21"/>
+      <c r="C45" s="88"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
@@ -2715,12 +2739,12 @@
     </row>
     <row r="46" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="20">
         <v>3500</v>
       </c>
-      <c r="C46" s="21">
+      <c r="C46" s="88">
         <v>3100</v>
       </c>
       <c r="D46" s="21">
@@ -2750,12 +2774,12 @@
     </row>
     <row r="47" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B47" s="20">
         <v>3160</v>
       </c>
-      <c r="C47" s="21">
+      <c r="C47" s="88">
         <v>2800</v>
       </c>
       <c r="D47" s="21">
@@ -2785,12 +2809,12 @@
     </row>
     <row r="48" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B48" s="20">
         <v>2900</v>
       </c>
-      <c r="C48" s="21">
+      <c r="C48" s="88">
         <v>2580</v>
       </c>
       <c r="D48" s="21">
@@ -2832,16 +2856,16 @@
       <c r="K49" s="15"/>
     </row>
     <row r="50" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="81" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="81"/>
-      <c r="C50" s="81"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="81"/>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
+      <c r="A50" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="86"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="86"/>
+      <c r="F50" s="86"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="86"/>
     </row>
     <row r="51" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
@@ -2874,7 +2898,7 @@
     </row>
     <row r="52" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="B52" s="18">
         <f>C23/C18</f>
@@ -2911,7 +2935,7 @@
     </row>
     <row r="53" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" s="41">
         <v>1</v>
@@ -2950,74 +2974,74 @@
       <c r="I54" s="46"/>
     </row>
     <row r="55" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="74"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="74"/>
+      <c r="A55" s="82" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="82"/>
+      <c r="C55" s="82"/>
+      <c r="D55" s="82"/>
+      <c r="E55" s="82"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="82"/>
+      <c r="H55" s="82"/>
+      <c r="I55" s="82"/>
     </row>
     <row r="56" spans="1:11" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="82" t="s">
+      <c r="A56" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="B56" s="82" t="s">
+      <c r="C56" s="75"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="C56" s="82"/>
-      <c r="D56" s="82"/>
-      <c r="E56" s="82"/>
-      <c r="F56" s="82" t="s">
-        <v>16</v>
-      </c>
-      <c r="G56" s="82"/>
+      <c r="G56" s="75"/>
       <c r="H56" s="27"/>
       <c r="I56" s="27"/>
     </row>
     <row r="57" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="82"/>
-      <c r="B57" s="83" t="s">
+      <c r="A57" s="75"/>
+      <c r="B57" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="75" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="75"/>
+      <c r="E57" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" s="82"/>
-      <c r="E57" s="83" t="s">
+      <c r="F57" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="G57" s="75" t="s">
         <v>18</v>
-      </c>
-      <c r="F57" s="82" t="s">
-        <v>57</v>
-      </c>
-      <c r="G57" s="82" t="s">
-        <v>19</v>
       </c>
       <c r="H57" s="27"/>
       <c r="I57" s="27"/>
     </row>
     <row r="58" spans="1:11" ht="48.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="82"/>
-      <c r="B58" s="83"/>
+      <c r="A58" s="75"/>
+      <c r="B58" s="74"/>
       <c r="C58" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D58" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="83"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="82"/>
+      <c r="E58" s="74"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="75"/>
       <c r="H58" s="27"/>
       <c r="I58" s="27"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
@@ -3030,7 +3054,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B60" s="32">
         <f>C35</f>
@@ -3061,7 +3085,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B61" s="32">
         <f>C36</f>
@@ -3092,7 +3116,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B62" s="29"/>
       <c r="C62" s="37">
@@ -3120,7 +3144,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B63" s="31"/>
       <c r="C63" s="31"/>
@@ -3133,7 +3157,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B64" s="32">
         <f>C37</f>
@@ -3163,7 +3187,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65" s="32">
         <f>C38</f>
@@ -3193,7 +3217,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B66" s="39"/>
       <c r="C66" s="38">
@@ -3221,7 +3245,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
@@ -3234,7 +3258,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B68" s="32">
         <f>C39</f>
@@ -3265,7 +3289,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B69" s="32">
         <f>C40</f>
@@ -3296,7 +3320,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="37">
@@ -3324,7 +3348,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B71" s="29"/>
       <c r="C71" s="40">
@@ -3351,19 +3375,19 @@
       <c r="I71" s="28"/>
     </row>
     <row r="73" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="73" t="s">
-        <v>61</v>
-      </c>
-      <c r="B73" s="73"/>
-      <c r="C73" s="73"/>
-      <c r="D73" s="73"/>
+      <c r="A73" s="81" t="s">
+        <v>60</v>
+      </c>
+      <c r="B73" s="81"/>
+      <c r="C73" s="81"/>
+      <c r="D73" s="81"/>
     </row>
     <row r="74" spans="1:9" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="82" t="s">
-        <v>60</v>
+      <c r="A74" s="75" t="s">
+        <v>59</v>
       </c>
       <c r="B74" s="78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C74" s="79"/>
       <c r="D74" s="80"/>
@@ -3371,22 +3395,22 @@
       <c r="F74" s="27"/>
     </row>
     <row r="75" spans="1:9" ht="48.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="82"/>
+      <c r="A75" s="75"/>
       <c r="B75" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="E75" s="28"/>
       <c r="F75" s="2"/>
     </row>
     <row r="76" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B76" s="8">
         <f>G62</f>
@@ -3405,7 +3429,7 @@
     </row>
     <row r="77" spans="1:9" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B77" s="8">
         <f>B76*C24/100</f>
@@ -3424,7 +3448,7 @@
     </row>
     <row r="78" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B78" s="8">
         <f>B76/3*20/100</f>
@@ -3438,12 +3462,12 @@
         <f t="shared" si="0"/>
         <v>4825.6000000000004</v>
       </c>
-      <c r="E78" s="84"/>
-      <c r="F78" s="85"/>
+      <c r="E78" s="76"/>
+      <c r="F78" s="77"/>
     </row>
     <row r="79" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B79" s="8">
         <f>B76/3*40/100</f>
@@ -3457,12 +3481,12 @@
         <f>D76/3*(40/100)</f>
         <v>9651.2000000000007</v>
       </c>
-      <c r="E79" s="84"/>
-      <c r="F79" s="85"/>
+      <c r="E79" s="76"/>
+      <c r="F79" s="77"/>
     </row>
     <row r="80" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B80" s="49">
         <f>SUM(B76:B79)</f>
@@ -3481,7 +3505,7 @@
     </row>
     <row r="81" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B81" s="52">
         <f>(C9-(C11+C12))/C14*100</f>
@@ -3500,7 +3524,7 @@
     </row>
     <row r="82" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B82" s="49">
         <f>B80*B81/100</f>
@@ -3519,7 +3543,7 @@
     </row>
     <row r="83" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B83" s="67">
         <f>SUM(B80,B82)</f>
@@ -3537,28 +3561,28 @@
       <c r="F83" s="27"/>
     </row>
     <row r="85" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B85" s="74"/>
-      <c r="C85" s="74"/>
-      <c r="D85" s="74"/>
-      <c r="E85" s="74"/>
-      <c r="F85" s="74"/>
-      <c r="G85" s="74"/>
+      <c r="A85" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" s="82"/>
+      <c r="C85" s="82"/>
+      <c r="D85" s="82"/>
+      <c r="E85" s="82"/>
+      <c r="F85" s="82"/>
+      <c r="G85" s="82"/>
     </row>
     <row r="86" spans="1:7" ht="26.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B86" s="83" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="82" t="s">
         <v>64</v>
       </c>
+      <c r="B86" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86" s="75" t="s">
+        <v>63</v>
+      </c>
       <c r="D86" s="78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E86" s="79"/>
       <c r="F86" s="79"/>
@@ -3566,24 +3590,24 @@
     </row>
     <row r="87" spans="1:7" ht="53.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
-      <c r="B87" s="83"/>
-      <c r="C87" s="82"/>
+      <c r="B87" s="74"/>
+      <c r="C87" s="75"/>
       <c r="D87" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B88" s="8">
         <f>C42</f>
@@ -3612,7 +3636,7 @@
     </row>
     <row r="89" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B89" s="8">
         <f t="shared" ref="B89:B90" si="3">C43</f>
@@ -3641,7 +3665,7 @@
     </row>
     <row r="90" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B90" s="8">
         <f t="shared" si="3"/>
@@ -3670,7 +3694,7 @@
     </row>
     <row r="91" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B91" s="49">
         <f>SUM(B88:B90)</f>
@@ -3696,12 +3720,12 @@
     </row>
     <row r="93" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>1</v>
@@ -3709,7 +3733,7 @@
     </row>
     <row r="95" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B95" s="54">
         <f>SUM(G91,B83,C83,D83)</f>
@@ -3718,7 +3742,7 @@
     </row>
     <row r="96" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B96" s="54">
         <f>SUM(B91,E71)</f>
@@ -3727,7 +3751,7 @@
     </row>
     <row r="97" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B97" s="55">
         <f>B95/B96</f>
@@ -3736,7 +3760,7 @@
     </row>
     <row r="98" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B98" s="55">
         <f>B97/12</f>
@@ -3745,7 +3769,7 @@
     </row>
     <row r="99" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B99" s="55">
         <f>C26/B96</f>
@@ -3754,7 +3778,7 @@
     </row>
     <row r="100" spans="1:2" ht="29.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B100" s="55">
         <f>B101*8</f>
@@ -3763,7 +3787,7 @@
     </row>
     <row r="101" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B101" s="55">
         <f>C26/B96/C17</f>
@@ -3771,167 +3795,152 @@
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" s="86" t="s">
-        <v>112</v>
-      </c>
-      <c r="B118" s="86"/>
-      <c r="C118" s="86"/>
-      <c r="D118" s="86"/>
-      <c r="E118" s="86"/>
-      <c r="F118" s="86"/>
-      <c r="G118" s="86"/>
-      <c r="H118" s="86"/>
-      <c r="I118" s="86"/>
+      <c r="A118" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="B118" s="73"/>
+      <c r="C118" s="73"/>
+      <c r="D118" s="73"/>
+      <c r="E118" s="73"/>
+      <c r="F118" s="73"/>
+      <c r="G118" s="73"/>
+      <c r="H118" s="73"/>
+      <c r="I118" s="73"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119" s="86"/>
-      <c r="B119" s="86"/>
-      <c r="C119" s="86"/>
-      <c r="D119" s="86"/>
-      <c r="E119" s="86"/>
-      <c r="F119" s="86"/>
-      <c r="G119" s="86"/>
-      <c r="H119" s="86"/>
-      <c r="I119" s="86"/>
+      <c r="A119" s="73"/>
+      <c r="B119" s="73"/>
+      <c r="C119" s="73"/>
+      <c r="D119" s="73"/>
+      <c r="E119" s="73"/>
+      <c r="F119" s="73"/>
+      <c r="G119" s="73"/>
+      <c r="H119" s="73"/>
+      <c r="I119" s="73"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" s="86"/>
-      <c r="B120" s="86"/>
-      <c r="C120" s="86"/>
-      <c r="D120" s="86"/>
-      <c r="E120" s="86"/>
-      <c r="F120" s="86"/>
-      <c r="G120" s="86"/>
-      <c r="H120" s="86"/>
-      <c r="I120" s="86"/>
+      <c r="A120" s="73"/>
+      <c r="B120" s="73"/>
+      <c r="C120" s="73"/>
+      <c r="D120" s="73"/>
+      <c r="E120" s="73"/>
+      <c r="F120" s="73"/>
+      <c r="G120" s="73"/>
+      <c r="H120" s="73"/>
+      <c r="I120" s="73"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" s="86"/>
-      <c r="B121" s="86"/>
-      <c r="C121" s="86"/>
-      <c r="D121" s="86"/>
-      <c r="E121" s="86"/>
-      <c r="F121" s="86"/>
-      <c r="G121" s="86"/>
-      <c r="H121" s="86"/>
-      <c r="I121" s="86"/>
+      <c r="A121" s="73"/>
+      <c r="B121" s="73"/>
+      <c r="C121" s="73"/>
+      <c r="D121" s="73"/>
+      <c r="E121" s="73"/>
+      <c r="F121" s="73"/>
+      <c r="G121" s="73"/>
+      <c r="H121" s="73"/>
+      <c r="I121" s="73"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122" s="86"/>
-      <c r="B122" s="86"/>
-      <c r="C122" s="86"/>
-      <c r="D122" s="86"/>
-      <c r="E122" s="86"/>
-      <c r="F122" s="86"/>
-      <c r="G122" s="86"/>
-      <c r="H122" s="86"/>
-      <c r="I122" s="86"/>
+      <c r="A122" s="73"/>
+      <c r="B122" s="73"/>
+      <c r="C122" s="73"/>
+      <c r="D122" s="73"/>
+      <c r="E122" s="73"/>
+      <c r="F122" s="73"/>
+      <c r="G122" s="73"/>
+      <c r="H122" s="73"/>
+      <c r="I122" s="73"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123" s="86"/>
-      <c r="B123" s="86"/>
-      <c r="C123" s="86"/>
-      <c r="D123" s="86"/>
-      <c r="E123" s="86"/>
-      <c r="F123" s="86"/>
-      <c r="G123" s="86"/>
-      <c r="H123" s="86"/>
-      <c r="I123" s="86"/>
+      <c r="A123" s="73"/>
+      <c r="B123" s="73"/>
+      <c r="C123" s="73"/>
+      <c r="D123" s="73"/>
+      <c r="E123" s="73"/>
+      <c r="F123" s="73"/>
+      <c r="G123" s="73"/>
+      <c r="H123" s="73"/>
+      <c r="I123" s="73"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" s="86"/>
-      <c r="B124" s="86"/>
-      <c r="C124" s="86"/>
-      <c r="D124" s="86"/>
-      <c r="E124" s="86"/>
-      <c r="F124" s="86"/>
-      <c r="G124" s="86"/>
-      <c r="H124" s="86"/>
-      <c r="I124" s="86"/>
+      <c r="A124" s="73"/>
+      <c r="B124" s="73"/>
+      <c r="C124" s="73"/>
+      <c r="D124" s="73"/>
+      <c r="E124" s="73"/>
+      <c r="F124" s="73"/>
+      <c r="G124" s="73"/>
+      <c r="H124" s="73"/>
+      <c r="I124" s="73"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" s="86"/>
-      <c r="B125" s="86"/>
-      <c r="C125" s="86"/>
-      <c r="D125" s="86"/>
-      <c r="E125" s="86"/>
-      <c r="F125" s="86"/>
-      <c r="G125" s="86"/>
-      <c r="H125" s="86"/>
-      <c r="I125" s="86"/>
+      <c r="A125" s="73"/>
+      <c r="B125" s="73"/>
+      <c r="C125" s="73"/>
+      <c r="D125" s="73"/>
+      <c r="E125" s="73"/>
+      <c r="F125" s="73"/>
+      <c r="G125" s="73"/>
+      <c r="H125" s="73"/>
+      <c r="I125" s="73"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="86"/>
-      <c r="B126" s="86"/>
-      <c r="C126" s="86"/>
-      <c r="D126" s="86"/>
-      <c r="E126" s="86"/>
-      <c r="F126" s="86"/>
-      <c r="G126" s="86"/>
-      <c r="H126" s="86"/>
-      <c r="I126" s="86"/>
+      <c r="A126" s="73"/>
+      <c r="B126" s="73"/>
+      <c r="C126" s="73"/>
+      <c r="D126" s="73"/>
+      <c r="E126" s="73"/>
+      <c r="F126" s="73"/>
+      <c r="G126" s="73"/>
+      <c r="H126" s="73"/>
+      <c r="I126" s="73"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="86"/>
-      <c r="B127" s="86"/>
-      <c r="C127" s="86"/>
-      <c r="D127" s="86"/>
-      <c r="E127" s="86"/>
-      <c r="F127" s="86"/>
-      <c r="G127" s="86"/>
-      <c r="H127" s="86"/>
-      <c r="I127" s="86"/>
+      <c r="A127" s="73"/>
+      <c r="B127" s="73"/>
+      <c r="C127" s="73"/>
+      <c r="D127" s="73"/>
+      <c r="E127" s="73"/>
+      <c r="F127" s="73"/>
+      <c r="G127" s="73"/>
+      <c r="H127" s="73"/>
+      <c r="I127" s="73"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="86"/>
-      <c r="B128" s="86"/>
-      <c r="C128" s="86"/>
-      <c r="D128" s="86"/>
-      <c r="E128" s="86"/>
-      <c r="F128" s="86"/>
-      <c r="G128" s="86"/>
-      <c r="H128" s="86"/>
-      <c r="I128" s="86"/>
+      <c r="A128" s="73"/>
+      <c r="B128" s="73"/>
+      <c r="C128" s="73"/>
+      <c r="D128" s="73"/>
+      <c r="E128" s="73"/>
+      <c r="F128" s="73"/>
+      <c r="G128" s="73"/>
+      <c r="H128" s="73"/>
+      <c r="I128" s="73"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A129" s="86"/>
-      <c r="B129" s="86"/>
-      <c r="C129" s="86"/>
-      <c r="D129" s="86"/>
-      <c r="E129" s="86"/>
-      <c r="F129" s="86"/>
-      <c r="G129" s="86"/>
-      <c r="H129" s="86"/>
-      <c r="I129" s="86"/>
+      <c r="A129" s="73"/>
+      <c r="B129" s="73"/>
+      <c r="C129" s="73"/>
+      <c r="D129" s="73"/>
+      <c r="E129" s="73"/>
+      <c r="F129" s="73"/>
+      <c r="G129" s="73"/>
+      <c r="H129" s="73"/>
+      <c r="I129" s="73"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A130" s="86"/>
-      <c r="B130" s="86"/>
-      <c r="C130" s="86"/>
-      <c r="D130" s="86"/>
-      <c r="E130" s="86"/>
-      <c r="F130" s="86"/>
-      <c r="G130" s="86"/>
-      <c r="H130" s="86"/>
-      <c r="I130" s="86"/>
+      <c r="A130" s="73"/>
+      <c r="B130" s="73"/>
+      <c r="C130" s="73"/>
+      <c r="D130" s="73"/>
+      <c r="E130" s="73"/>
+      <c r="F130" s="73"/>
+      <c r="G130" s="73"/>
+      <c r="H130" s="73"/>
+      <c r="I130" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A118:I130"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="D86:G86"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A85:G85"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="B21:K21"/>
     <mergeCell ref="A55:I55"/>
     <mergeCell ref="B56:E56"/>
     <mergeCell ref="F56:G56"/>
@@ -3941,6 +3950,21 @@
     <mergeCell ref="E57:E58"/>
     <mergeCell ref="F57:F58"/>
     <mergeCell ref="G57:G58"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="D86:G86"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A85:G85"/>
+    <mergeCell ref="A118:I130"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:F79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -3949,7 +3973,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="110.33203125" customWidth="1"/>
@@ -3957,17 +3981,17 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="63" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A3" s="59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
@@ -3975,7 +3999,7 @@
     </row>
     <row r="5" spans="1:1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A5" s="61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
@@ -3983,7 +4007,7 @@
     </row>
     <row r="7" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
@@ -3991,17 +4015,17 @@
     </row>
     <row r="9" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A11" s="59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
@@ -4009,57 +4033,62 @@
     </row>
     <row r="13" spans="1:1" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A13" s="66" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A14" s="69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A16" s="68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="78" x14ac:dyDescent="0.3">
       <c r="A19" s="70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.4">
       <c r="A22" s="72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.4">
       <c r="A23" s="72" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A24" s="71" t="s">
-        <v>105</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/3k2s/Экономика IT-компании/Лабораторная работа 2_ФОТ_с.xlsx
+++ b/3k2s/Экономика IT-компании/Лабораторная работа 2_ФОТ_с.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="Задание исх данные, решение 1" sheetId="1" r:id="rId1"/>
@@ -1175,62 +1175,62 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1532,43 +1532,43 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="85"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="83"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="80"/>
+      <c r="B4" s="84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="86"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="56">
         <v>1</v>
       </c>
-      <c r="C5" s="87">
+      <c r="C5" s="73">
         <v>2</v>
       </c>
       <c r="D5" s="57">
@@ -1603,7 +1603,7 @@
       <c r="B6" s="7">
         <v>365</v>
       </c>
-      <c r="C6" s="88">
+      <c r="C6" s="74">
         <v>365</v>
       </c>
       <c r="D6" s="7">
@@ -1638,7 +1638,7 @@
       <c r="B7" s="7">
         <v>113</v>
       </c>
-      <c r="C7" s="88">
+      <c r="C7" s="74">
         <v>112</v>
       </c>
       <c r="D7" s="7">
@@ -1671,7 +1671,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="8"/>
-      <c r="C8" s="88">
+      <c r="C8" s="74">
         <f>C6-C7</f>
         <v>253</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>36</v>
       </c>
       <c r="B9" s="8"/>
-      <c r="C9" s="88">
+      <c r="C9" s="74">
         <f>SUM(C10:C13)</f>
         <v>32</v>
       </c>
@@ -1709,7 +1709,7 @@
       <c r="B10" s="7">
         <v>26</v>
       </c>
-      <c r="C10" s="89">
+      <c r="C10" s="75">
         <v>28</v>
       </c>
       <c r="D10" s="9">
@@ -1744,7 +1744,7 @@
       <c r="B11" s="7">
         <v>3</v>
       </c>
-      <c r="C11" s="89">
+      <c r="C11" s="75">
         <v>1</v>
       </c>
       <c r="D11" s="9">
@@ -1779,7 +1779,7 @@
       <c r="B12" s="7">
         <v>3</v>
       </c>
-      <c r="C12" s="89">
+      <c r="C12" s="75">
         <v>2</v>
       </c>
       <c r="D12" s="9">
@@ -1814,7 +1814,7 @@
       <c r="B13" s="7">
         <v>2</v>
       </c>
-      <c r="C13" s="88">
+      <c r="C13" s="74">
         <v>1</v>
       </c>
       <c r="D13" s="7">
@@ -1847,7 +1847,7 @@
         <v>110</v>
       </c>
       <c r="B14" s="8"/>
-      <c r="C14" s="88">
+      <c r="C14" s="74">
         <f>C8-C9</f>
         <v>221</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="8"/>
-      <c r="C15" s="88">
+      <c r="C15" s="74">
         <f>C14*8</f>
         <v>1768</v>
       </c>
@@ -1885,7 +1885,7 @@
       <c r="B16" s="7">
         <v>10</v>
       </c>
-      <c r="C16" s="88">
+      <c r="C16" s="74">
         <v>9</v>
       </c>
       <c r="D16" s="7">
@@ -1918,7 +1918,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="8"/>
-      <c r="C17" s="88">
+      <c r="C17" s="74">
         <f>C15-C16</f>
         <v>1759</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>82</v>
       </c>
       <c r="B18" s="8"/>
-      <c r="C18" s="88">
+      <c r="C18" s="74">
         <f>C17/12</f>
         <v>146.58333333333334</v>
       </c>
@@ -1950,40 +1950,40 @@
       <c r="K18" s="8"/>
     </row>
     <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
     </row>
     <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="80"/>
+      <c r="B21" s="84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="86"/>
     </row>
     <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="56">
         <v>1</v>
       </c>
-      <c r="C22" s="87">
+      <c r="C22" s="73">
         <v>2</v>
       </c>
       <c r="D22" s="57">
@@ -2018,7 +2018,7 @@
       <c r="B23" s="7">
         <v>600</v>
       </c>
-      <c r="C23" s="88">
+      <c r="C23" s="74">
         <v>520</v>
       </c>
       <c r="D23" s="7">
@@ -2053,7 +2053,7 @@
       <c r="B24" s="7">
         <v>50</v>
       </c>
-      <c r="C24" s="88">
+      <c r="C24" s="74">
         <v>55</v>
       </c>
       <c r="D24" s="7">
@@ -2088,7 +2088,7 @@
       <c r="B25" s="7">
         <v>2</v>
       </c>
-      <c r="C25" s="88">
+      <c r="C25" s="74">
         <v>3</v>
       </c>
       <c r="D25" s="7">
@@ -2123,7 +2123,7 @@
       <c r="B26" s="7">
         <v>13380</v>
       </c>
-      <c r="C26" s="88">
+      <c r="C26" s="74">
         <v>15960</v>
       </c>
       <c r="D26" s="7">
@@ -2156,7 +2156,7 @@
         <v>48</v>
       </c>
       <c r="B27" s="16"/>
-      <c r="C27" s="90"/>
+      <c r="C27" s="76"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
@@ -2173,7 +2173,7 @@
       <c r="B28" s="20">
         <v>1</v>
       </c>
-      <c r="C28" s="88">
+      <c r="C28" s="74">
         <v>2</v>
       </c>
       <c r="D28" s="21">
@@ -2208,7 +2208,7 @@
       <c r="B29" s="20">
         <v>5</v>
       </c>
-      <c r="C29" s="88">
+      <c r="C29" s="74">
         <v>4</v>
       </c>
       <c r="D29" s="21">
@@ -2243,7 +2243,7 @@
       <c r="B30" s="20">
         <v>1</v>
       </c>
-      <c r="C30" s="88">
+      <c r="C30" s="74">
         <v>1</v>
       </c>
       <c r="D30" s="21">
@@ -2278,7 +2278,7 @@
       <c r="B31" s="20">
         <v>1</v>
       </c>
-      <c r="C31" s="88">
+      <c r="C31" s="74">
         <v>2</v>
       </c>
       <c r="D31" s="21">
@@ -2313,7 +2313,7 @@
       <c r="B32" s="20">
         <v>2</v>
       </c>
-      <c r="C32" s="88">
+      <c r="C32" s="74">
         <v>2</v>
       </c>
       <c r="D32" s="21">
@@ -2348,7 +2348,7 @@
       <c r="B33" s="20">
         <v>3</v>
       </c>
-      <c r="C33" s="88">
+      <c r="C33" s="74">
         <v>1</v>
       </c>
       <c r="D33" s="21">
@@ -2381,7 +2381,7 @@
         <v>55</v>
       </c>
       <c r="B34" s="23"/>
-      <c r="C34" s="91"/>
+      <c r="C34" s="77"/>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
       <c r="F34" s="24"/>
@@ -2398,7 +2398,7 @@
       <c r="B35" s="23">
         <v>6</v>
       </c>
-      <c r="C35" s="91">
+      <c r="C35" s="77">
         <v>7</v>
       </c>
       <c r="D35" s="24">
@@ -2433,7 +2433,7 @@
       <c r="B36" s="23">
         <v>4</v>
       </c>
-      <c r="C36" s="91">
+      <c r="C36" s="77">
         <v>3</v>
       </c>
       <c r="D36" s="24">
@@ -2468,7 +2468,7 @@
       <c r="B37" s="23">
         <v>5</v>
       </c>
-      <c r="C37" s="91">
+      <c r="C37" s="77">
         <v>5</v>
       </c>
       <c r="D37" s="24">
@@ -2503,7 +2503,7 @@
       <c r="B38" s="23">
         <v>7</v>
       </c>
-      <c r="C38" s="91">
+      <c r="C38" s="77">
         <v>6</v>
       </c>
       <c r="D38" s="24">
@@ -2538,7 +2538,7 @@
       <c r="B39" s="23">
         <v>3</v>
       </c>
-      <c r="C39" s="91">
+      <c r="C39" s="77">
         <v>2</v>
       </c>
       <c r="D39" s="24">
@@ -2573,7 +2573,7 @@
       <c r="B40" s="23">
         <v>2</v>
       </c>
-      <c r="C40" s="91">
+      <c r="C40" s="77">
         <v>2</v>
       </c>
       <c r="D40" s="24">
@@ -2606,7 +2606,7 @@
         <v>65</v>
       </c>
       <c r="B41" s="20"/>
-      <c r="C41" s="88"/>
+      <c r="C41" s="74"/>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
@@ -2623,7 +2623,7 @@
       <c r="B42" s="20">
         <v>1</v>
       </c>
-      <c r="C42" s="88">
+      <c r="C42" s="74">
         <v>2</v>
       </c>
       <c r="D42" s="21">
@@ -2658,7 +2658,7 @@
       <c r="B43" s="20">
         <v>1</v>
       </c>
-      <c r="C43" s="88">
+      <c r="C43" s="74">
         <v>2</v>
       </c>
       <c r="D43" s="21">
@@ -2693,7 +2693,7 @@
       <c r="B44" s="20">
         <v>2</v>
       </c>
-      <c r="C44" s="88">
+      <c r="C44" s="74">
         <v>3</v>
       </c>
       <c r="D44" s="21">
@@ -2727,7 +2727,7 @@
         <v>63</v>
       </c>
       <c r="B45" s="20"/>
-      <c r="C45" s="88"/>
+      <c r="C45" s="74"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
@@ -2744,7 +2744,7 @@
       <c r="B46" s="20">
         <v>3500</v>
       </c>
-      <c r="C46" s="88">
+      <c r="C46" s="74">
         <v>3100</v>
       </c>
       <c r="D46" s="21">
@@ -2779,7 +2779,7 @@
       <c r="B47" s="20">
         <v>3160</v>
       </c>
-      <c r="C47" s="88">
+      <c r="C47" s="74">
         <v>2800</v>
       </c>
       <c r="D47" s="21">
@@ -2814,7 +2814,7 @@
       <c r="B48" s="20">
         <v>2900</v>
       </c>
-      <c r="C48" s="88">
+      <c r="C48" s="74">
         <v>2580</v>
       </c>
       <c r="D48" s="21">
@@ -2856,16 +2856,16 @@
       <c r="K49" s="15"/>
     </row>
     <row r="50" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="86" t="s">
+      <c r="A50" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="86"/>
-      <c r="C50" s="86"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="86"/>
-      <c r="F50" s="86"/>
-      <c r="G50" s="86"/>
-      <c r="H50" s="86"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="87"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="87"/>
+      <c r="F50" s="87"/>
+      <c r="G50" s="87"/>
+      <c r="H50" s="87"/>
     </row>
     <row r="51" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
@@ -2974,68 +2974,68 @@
       <c r="I54" s="46"/>
     </row>
     <row r="55" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="82" t="s">
+      <c r="A55" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="B55" s="82"/>
-      <c r="C55" s="82"/>
-      <c r="D55" s="82"/>
-      <c r="E55" s="82"/>
-      <c r="F55" s="82"/>
-      <c r="G55" s="82"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="82"/>
+      <c r="B55" s="78"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="78"/>
+      <c r="E55" s="78"/>
+      <c r="F55" s="78"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="78"/>
+      <c r="I55" s="78"/>
     </row>
     <row r="56" spans="1:11" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="75" t="s">
+      <c r="A56" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="75" t="s">
+      <c r="B56" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="C56" s="75"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="75" t="s">
+      <c r="C56" s="79"/>
+      <c r="D56" s="79"/>
+      <c r="E56" s="79"/>
+      <c r="F56" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="G56" s="75"/>
+      <c r="G56" s="79"/>
       <c r="H56" s="27"/>
       <c r="I56" s="27"/>
     </row>
     <row r="57" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="75"/>
-      <c r="B57" s="74" t="s">
+      <c r="A57" s="79"/>
+      <c r="B57" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="75" t="s">
+      <c r="C57" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="75"/>
-      <c r="E57" s="74" t="s">
+      <c r="D57" s="79"/>
+      <c r="E57" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="F57" s="75" t="s">
+      <c r="F57" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="G57" s="75" t="s">
+      <c r="G57" s="79" t="s">
         <v>18</v>
       </c>
       <c r="H57" s="27"/>
       <c r="I57" s="27"/>
     </row>
     <row r="58" spans="1:11" ht="48.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="75"/>
-      <c r="B58" s="74"/>
+      <c r="A58" s="79"/>
+      <c r="B58" s="80"/>
       <c r="C58" s="44" t="s">
         <v>19</v>
       </c>
       <c r="D58" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E58" s="74"/>
-      <c r="F58" s="75"/>
-      <c r="G58" s="75"/>
+      <c r="E58" s="80"/>
+      <c r="F58" s="79"/>
+      <c r="G58" s="79"/>
       <c r="H58" s="27"/>
       <c r="I58" s="27"/>
     </row>
@@ -3375,27 +3375,27 @@
       <c r="I71" s="28"/>
     </row>
     <row r="73" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="81" t="s">
+      <c r="A73" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="B73" s="81"/>
-      <c r="C73" s="81"/>
-      <c r="D73" s="81"/>
+      <c r="B73" s="88"/>
+      <c r="C73" s="88"/>
+      <c r="D73" s="88"/>
     </row>
     <row r="74" spans="1:9" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="75" t="s">
+      <c r="A74" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="B74" s="78" t="s">
+      <c r="B74" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="79"/>
-      <c r="D74" s="80"/>
+      <c r="C74" s="85"/>
+      <c r="D74" s="86"/>
       <c r="E74" s="27"/>
       <c r="F74" s="27"/>
     </row>
     <row r="75" spans="1:9" ht="48.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="75"/>
+      <c r="A75" s="79"/>
       <c r="B75" s="4" t="s">
         <v>58</v>
       </c>
@@ -3462,8 +3462,8 @@
         <f t="shared" si="0"/>
         <v>4825.6000000000004</v>
       </c>
-      <c r="E78" s="76"/>
-      <c r="F78" s="77"/>
+      <c r="E78" s="90"/>
+      <c r="F78" s="91"/>
     </row>
     <row r="79" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
@@ -3481,8 +3481,8 @@
         <f>D76/3*(40/100)</f>
         <v>9651.2000000000007</v>
       </c>
-      <c r="E79" s="76"/>
-      <c r="F79" s="77"/>
+      <c r="E79" s="90"/>
+      <c r="F79" s="91"/>
     </row>
     <row r="80" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
@@ -3561,37 +3561,37 @@
       <c r="F83" s="27"/>
     </row>
     <row r="85" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="82" t="s">
+      <c r="A85" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="B85" s="82"/>
-      <c r="C85" s="82"/>
-      <c r="D85" s="82"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="82"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="78"/>
+      <c r="D85" s="78"/>
+      <c r="E85" s="78"/>
+      <c r="F85" s="78"/>
+      <c r="G85" s="78"/>
     </row>
     <row r="86" spans="1:7" ht="26.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B86" s="74" t="s">
+      <c r="B86" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="75" t="s">
+      <c r="C86" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="D86" s="78" t="s">
+      <c r="D86" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="E86" s="79"/>
-      <c r="F86" s="79"/>
-      <c r="G86" s="80"/>
+      <c r="E86" s="85"/>
+      <c r="F86" s="85"/>
+      <c r="G86" s="86"/>
     </row>
     <row r="87" spans="1:7" ht="53.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
-      <c r="B87" s="74"/>
-      <c r="C87" s="75"/>
+      <c r="B87" s="80"/>
+      <c r="C87" s="79"/>
       <c r="D87" s="4" t="s">
         <v>62</v>
       </c>
@@ -3790,157 +3790,172 @@
         <v>76</v>
       </c>
       <c r="B101" s="55">
-        <f>C26/B96/C17</f>
+        <f>B99/C17</f>
         <v>0.18902785673678227</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" s="73" t="s">
+      <c r="A118" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="B118" s="73"/>
-      <c r="C118" s="73"/>
-      <c r="D118" s="73"/>
-      <c r="E118" s="73"/>
-      <c r="F118" s="73"/>
-      <c r="G118" s="73"/>
-      <c r="H118" s="73"/>
-      <c r="I118" s="73"/>
+      <c r="B118" s="89"/>
+      <c r="C118" s="89"/>
+      <c r="D118" s="89"/>
+      <c r="E118" s="89"/>
+      <c r="F118" s="89"/>
+      <c r="G118" s="89"/>
+      <c r="H118" s="89"/>
+      <c r="I118" s="89"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119" s="73"/>
-      <c r="B119" s="73"/>
-      <c r="C119" s="73"/>
-      <c r="D119" s="73"/>
-      <c r="E119" s="73"/>
-      <c r="F119" s="73"/>
-      <c r="G119" s="73"/>
-      <c r="H119" s="73"/>
-      <c r="I119" s="73"/>
+      <c r="A119" s="89"/>
+      <c r="B119" s="89"/>
+      <c r="C119" s="89"/>
+      <c r="D119" s="89"/>
+      <c r="E119" s="89"/>
+      <c r="F119" s="89"/>
+      <c r="G119" s="89"/>
+      <c r="H119" s="89"/>
+      <c r="I119" s="89"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" s="73"/>
-      <c r="B120" s="73"/>
-      <c r="C120" s="73"/>
-      <c r="D120" s="73"/>
-      <c r="E120" s="73"/>
-      <c r="F120" s="73"/>
-      <c r="G120" s="73"/>
-      <c r="H120" s="73"/>
-      <c r="I120" s="73"/>
+      <c r="A120" s="89"/>
+      <c r="B120" s="89"/>
+      <c r="C120" s="89"/>
+      <c r="D120" s="89"/>
+      <c r="E120" s="89"/>
+      <c r="F120" s="89"/>
+      <c r="G120" s="89"/>
+      <c r="H120" s="89"/>
+      <c r="I120" s="89"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" s="73"/>
-      <c r="B121" s="73"/>
-      <c r="C121" s="73"/>
-      <c r="D121" s="73"/>
-      <c r="E121" s="73"/>
-      <c r="F121" s="73"/>
-      <c r="G121" s="73"/>
-      <c r="H121" s="73"/>
-      <c r="I121" s="73"/>
+      <c r="A121" s="89"/>
+      <c r="B121" s="89"/>
+      <c r="C121" s="89"/>
+      <c r="D121" s="89"/>
+      <c r="E121" s="89"/>
+      <c r="F121" s="89"/>
+      <c r="G121" s="89"/>
+      <c r="H121" s="89"/>
+      <c r="I121" s="89"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122" s="73"/>
-      <c r="B122" s="73"/>
-      <c r="C122" s="73"/>
-      <c r="D122" s="73"/>
-      <c r="E122" s="73"/>
-      <c r="F122" s="73"/>
-      <c r="G122" s="73"/>
-      <c r="H122" s="73"/>
-      <c r="I122" s="73"/>
+      <c r="A122" s="89"/>
+      <c r="B122" s="89"/>
+      <c r="C122" s="89"/>
+      <c r="D122" s="89"/>
+      <c r="E122" s="89"/>
+      <c r="F122" s="89"/>
+      <c r="G122" s="89"/>
+      <c r="H122" s="89"/>
+      <c r="I122" s="89"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123" s="73"/>
-      <c r="B123" s="73"/>
-      <c r="C123" s="73"/>
-      <c r="D123" s="73"/>
-      <c r="E123" s="73"/>
-      <c r="F123" s="73"/>
-      <c r="G123" s="73"/>
-      <c r="H123" s="73"/>
-      <c r="I123" s="73"/>
+      <c r="A123" s="89"/>
+      <c r="B123" s="89"/>
+      <c r="C123" s="89"/>
+      <c r="D123" s="89"/>
+      <c r="E123" s="89"/>
+      <c r="F123" s="89"/>
+      <c r="G123" s="89"/>
+      <c r="H123" s="89"/>
+      <c r="I123" s="89"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" s="73"/>
-      <c r="B124" s="73"/>
-      <c r="C124" s="73"/>
-      <c r="D124" s="73"/>
-      <c r="E124" s="73"/>
-      <c r="F124" s="73"/>
-      <c r="G124" s="73"/>
-      <c r="H124" s="73"/>
-      <c r="I124" s="73"/>
+      <c r="A124" s="89"/>
+      <c r="B124" s="89"/>
+      <c r="C124" s="89"/>
+      <c r="D124" s="89"/>
+      <c r="E124" s="89"/>
+      <c r="F124" s="89"/>
+      <c r="G124" s="89"/>
+      <c r="H124" s="89"/>
+      <c r="I124" s="89"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" s="73"/>
-      <c r="B125" s="73"/>
-      <c r="C125" s="73"/>
-      <c r="D125" s="73"/>
-      <c r="E125" s="73"/>
-      <c r="F125" s="73"/>
-      <c r="G125" s="73"/>
-      <c r="H125" s="73"/>
-      <c r="I125" s="73"/>
+      <c r="A125" s="89"/>
+      <c r="B125" s="89"/>
+      <c r="C125" s="89"/>
+      <c r="D125" s="89"/>
+      <c r="E125" s="89"/>
+      <c r="F125" s="89"/>
+      <c r="G125" s="89"/>
+      <c r="H125" s="89"/>
+      <c r="I125" s="89"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="73"/>
-      <c r="B126" s="73"/>
-      <c r="C126" s="73"/>
-      <c r="D126" s="73"/>
-      <c r="E126" s="73"/>
-      <c r="F126" s="73"/>
-      <c r="G126" s="73"/>
-      <c r="H126" s="73"/>
-      <c r="I126" s="73"/>
+      <c r="A126" s="89"/>
+      <c r="B126" s="89"/>
+      <c r="C126" s="89"/>
+      <c r="D126" s="89"/>
+      <c r="E126" s="89"/>
+      <c r="F126" s="89"/>
+      <c r="G126" s="89"/>
+      <c r="H126" s="89"/>
+      <c r="I126" s="89"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="73"/>
-      <c r="B127" s="73"/>
-      <c r="C127" s="73"/>
-      <c r="D127" s="73"/>
-      <c r="E127" s="73"/>
-      <c r="F127" s="73"/>
-      <c r="G127" s="73"/>
-      <c r="H127" s="73"/>
-      <c r="I127" s="73"/>
+      <c r="A127" s="89"/>
+      <c r="B127" s="89"/>
+      <c r="C127" s="89"/>
+      <c r="D127" s="89"/>
+      <c r="E127" s="89"/>
+      <c r="F127" s="89"/>
+      <c r="G127" s="89"/>
+      <c r="H127" s="89"/>
+      <c r="I127" s="89"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="73"/>
-      <c r="B128" s="73"/>
-      <c r="C128" s="73"/>
-      <c r="D128" s="73"/>
-      <c r="E128" s="73"/>
-      <c r="F128" s="73"/>
-      <c r="G128" s="73"/>
-      <c r="H128" s="73"/>
-      <c r="I128" s="73"/>
+      <c r="A128" s="89"/>
+      <c r="B128" s="89"/>
+      <c r="C128" s="89"/>
+      <c r="D128" s="89"/>
+      <c r="E128" s="89"/>
+      <c r="F128" s="89"/>
+      <c r="G128" s="89"/>
+      <c r="H128" s="89"/>
+      <c r="I128" s="89"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A129" s="73"/>
-      <c r="B129" s="73"/>
-      <c r="C129" s="73"/>
-      <c r="D129" s="73"/>
-      <c r="E129" s="73"/>
-      <c r="F129" s="73"/>
-      <c r="G129" s="73"/>
-      <c r="H129" s="73"/>
-      <c r="I129" s="73"/>
+      <c r="A129" s="89"/>
+      <c r="B129" s="89"/>
+      <c r="C129" s="89"/>
+      <c r="D129" s="89"/>
+      <c r="E129" s="89"/>
+      <c r="F129" s="89"/>
+      <c r="G129" s="89"/>
+      <c r="H129" s="89"/>
+      <c r="I129" s="89"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A130" s="73"/>
-      <c r="B130" s="73"/>
-      <c r="C130" s="73"/>
-      <c r="D130" s="73"/>
-      <c r="E130" s="73"/>
-      <c r="F130" s="73"/>
-      <c r="G130" s="73"/>
-      <c r="H130" s="73"/>
-      <c r="I130" s="73"/>
+      <c r="A130" s="89"/>
+      <c r="B130" s="89"/>
+      <c r="C130" s="89"/>
+      <c r="D130" s="89"/>
+      <c r="E130" s="89"/>
+      <c r="F130" s="89"/>
+      <c r="G130" s="89"/>
+      <c r="H130" s="89"/>
+      <c r="I130" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A118:I130"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="D86:G86"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A85:G85"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="B21:K21"/>
     <mergeCell ref="A55:I55"/>
     <mergeCell ref="B56:E56"/>
     <mergeCell ref="F56:G56"/>
@@ -3950,21 +3965,6 @@
     <mergeCell ref="E57:E58"/>
     <mergeCell ref="F57:F58"/>
     <mergeCell ref="G57:G58"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="B21:K21"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="D86:G86"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A85:G85"/>
-    <mergeCell ref="A118:I130"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
